--- a/Schedule/BCIO-schedule-hierarchy.xlsx
+++ b/Schedule/BCIO-schedule-hierarchy.xlsx
@@ -441,32 +441,32 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>informaldefinition</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>synonyms</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>examples</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>crossreference</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>subontology</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>crossreference</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>examples</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>synonyms</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>informaldefinition</t>
         </is>
       </c>
     </row>
@@ -545,14 +545,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BFO:0000020</t>
+          <t>BFO:0000031</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>specifically dependent continuant</t>
+          <t>generically dependent continuant</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -562,14 +562,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>b is a specifically dependent continuant = Def. b is a continuant &amp; there is some independent continuant c which is not a spatial region and which is such that b s-depends_on c at every time t during the course of b’s existence. (axiom label in BFO2 Reference: [050-003])</t>
+          <t>b is a generically dependent continuant = Def. b is a continuant that g-depends_on one or more other entities. (axiom label in BFO2 Reference: [074-001])</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PATO:0000044</t>
+          <t>IAO:0000030</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -577,7 +577,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>frequency</t>
+          <t>information content entity</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -586,89 +586,110 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>A physical quality which inheres in a bearer by virtue of the number of the bearer's repetitive actions in a particular time.</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>A generically dependent continuant that is about some thing.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BFO:0000031</t>
+          <t>IAO:0000027</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>generically dependent continuant</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>data item</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>b is a generically dependent continuant = Def. b is a continuant that g-depends_on one or more other entities. (axiom label in BFO2 Reference: [074-001])</t>
+          <t>An information content entity that is intended to be a truthful statement about something (modulo, e.g., measurement precision or other systematic errors) and is constructed/acquired by a method which reliably tends to produce (approximately) truthful statements.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IAO:0000030</t>
+          <t>BCIO:008710</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>information content entity</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>BCI temporal part frequency</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>A generically dependent continuant that is about some thing.</t>
-        </is>
-      </c>
+          <t>A &lt;data item&gt; that is how often intervention temporal parts occur within a BCI.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>How often intervention parts are planned to occur</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>This is useful when grouping contact events together to the schedule of an intervention. For example, authors may describe participants as taking part in 90 minutes of physical activity weekly. These 90 minutes could be split across several contact events, however together these contact events form an intervention part which occurs weekly.; Participants took part in 90 minutes of PA "weekly"</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IAO:0000027</t>
+          <t>BCIO:008515</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>data item</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>number of BCI contact events</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>An information content entity that is intended to be a truthful statement about something (modulo, e.g., measurement precision or other systematic errors) and is constructed/acquired by a method which reliably tends to produce (approximately) truthful statements.</t>
-        </is>
-      </c>
+          <t>A &lt;data item&gt; that is the number of contact events in a BCI temporal part.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>The planned total number of sessions or digital contacts in an intervention or part</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>one; 6; 12; twenty</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BCIO:050504</t>
+          <t>BCIO:050905</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -678,24 +699,24 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>total BCI contact event duration statistic</t>
+          <t>BCI duration statistic</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>A &lt;data item&gt; that is about a collection of total contact event durations.</t>
+          <t>A &lt;data item&gt; that is about a collection of BCI durations.</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BCIO:050499</t>
+          <t>BCIO:050908</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -706,23 +727,23 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>median total BCI contact event duration</t>
+          <t>maximum BCI duration</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>A &lt;total contact event duration statistic&gt; that is the central value of a collection of total contact event durations when they are arranged in ascending order.</t>
+          <t>A &lt;BCI duration statistic&gt; that is the highest value from a collection of BCI durations.</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BCIO:050910</t>
+          <t>BCIO:050909</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -733,23 +754,23 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>maximum total BCI contact event duration</t>
+          <t>mean BCI duration</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>A &lt;total contact event duration statistic&gt; that is the highest value from a collection of total contact event durations.</t>
+          <t>A &lt;BCI duration statistic&gt; that is the average value calculated from a collection of BCI durations.</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BCIO:050495</t>
+          <t>BCIO:050501</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -760,23 +781,23 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>mean total BCI contact event duration</t>
+          <t>minimum BCI duration</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>A &lt;total contact event duration statistic&gt; that is the average value calculated from a collection of total contact event durations.</t>
+          <t>A &lt;BCI duration statistic&gt; that is the lowest value from a collection of BCI durations.</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BCIO:050503</t>
+          <t>BCIO:050498</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -787,23 +808,23 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>minimum total BCI contact event duration</t>
+          <t>median BCI duration</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>A &lt;total contact event duration statistic&gt; that is the lowest value from a collection of total contact event durations.</t>
+          <t>A &lt;BCI duration statistic&gt; that is the central value of a collection of BCI durations when they are arranged in ascending order.</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCIO:050516</t>
+          <t>BCIO:050504</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -813,24 +834,24 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>BCI temporal part frequency statistic</t>
+          <t>total BCI contact event duration statistic</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>A &lt;data item&gt; that is about a collection of BCI temporal part frequencies.</t>
+          <t>A &lt;data item&gt; that is about a collection of total contact event durations.</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BCIO:050518</t>
+          <t>BCIO:050499</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -841,23 +862,23 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>mean BCI temporal part frequency statistic</t>
+          <t>median total BCI contact event duration</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>A &lt;BCI temporal part frequency statistic&gt; that is the average value calculated from a collection of BCI temporal part frequencies.</t>
+          <t>A &lt;total contact event duration statistic&gt; that is the central value of a collection of total contact event durations when they are arranged in ascending order.</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BCIO:050520</t>
+          <t>BCIO:050910</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -868,23 +889,23 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>minimum BCI temporal part frequency statistic</t>
+          <t>maximum total BCI contact event duration</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>A &lt;BCI temporal part frequency statistic&gt; that is the lowest value from a collection of BCI temporal part frequencies.</t>
+          <t>A &lt;total contact event duration statistic&gt; that is the highest value from a collection of total contact event durations.</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BCIO:050519</t>
+          <t>BCIO:050495</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -895,23 +916,23 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>median BCI temporal part frequency statistic</t>
+          <t>mean total BCI contact event duration</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>A &lt;BCI temporal part frequency statistic&gt; that is the central value of a collection of BCI temporal part frequencies when they are arranged in ascending order.</t>
+          <t>A &lt;total contact event duration statistic&gt; that is the average value calculated from a collection of total contact event durations.</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BCIO:050517</t>
+          <t>BCIO:050503</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -922,18 +943,18 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>maximum BCI temporal part frequency statistic</t>
+          <t>minimum total BCI contact event duration</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>A &lt;BCI temporal part frequency statistic&gt; that is the highest value from a collection of BCI temporal part frequencies.</t>
+          <t>A &lt;total contact event duration statistic&gt; that is the lowest value from a collection of total contact event durations.</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -959,13 +980,13 @@
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BCIO:050510</t>
+          <t>BCIO:050508</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -976,23 +997,23 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>mean BCI temporal part duration</t>
+          <t>maximum BCI temporal part duration</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>A &lt;BCI temporal part duration statistic&gt; that is the average value calculated from a collection of BCI temporal part durations.</t>
+          <t>A &lt;BCI temporal part duration statistic&gt; that denotes the highest value from a collection of BCI temporal part durations.</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BCIO:050508</t>
+          <t>BCIO:050514</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1003,23 +1024,23 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>maximum BCI temporal part duration</t>
+          <t>minimum BCI temporal part duration</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>A &lt;BCI temporal part duration statistic&gt; that denotes the highest value from a collection of BCI temporal part durations.</t>
+          <t>A &lt;BCI temporal part duration statistic&gt; that denotes the lowest value from a collection of BCI temporal part durations.</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BCIO:050514</t>
+          <t>BCIO:050512</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1030,23 +1051,23 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>minimum BCI temporal part duration</t>
+          <t>median BCI temporal part duration</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>A &lt;BCI temporal part duration statistic&gt; that denotes the lowest value from a collection of BCI temporal part durations.</t>
+          <t>A &lt;BCI temporal part duration statistic&gt; that is the central value of a collection of BCI temporal part durations when they are arranged in ascending order.</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BCIO:050512</t>
+          <t>BCIO:050510</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1057,23 +1078,23 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>median BCI temporal part duration</t>
+          <t>mean BCI temporal part duration</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>A &lt;BCI temporal part duration statistic&gt; that is the central value of a collection of BCI temporal part durations when they are arranged in ascending order.</t>
+          <t>A &lt;BCI temporal part duration statistic&gt; that is the average value calculated from a collection of BCI temporal part durations.</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BCIO:050905</t>
+          <t>BCIO:050505</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1083,24 +1104,24 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>BCI duration statistic</t>
+          <t>BCI contact event duration statistic</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>A &lt;data item&gt; that is about a collection of BCI durations.</t>
+          <t>A &lt;data item&gt; that is about a collection of BCI contact event durations.</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BCIO:050909</t>
+          <t>BCIO:050513</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1111,23 +1132,23 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>mean BCI duration</t>
+          <t>minimum BCI contact event duration</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>A &lt;BCI duration statistic&gt; that is the average value calculated from a collection of BCI durations.</t>
+          <t>A &lt;BCI contact event duration statistic&gt; that is the lowest value from a collection of BCI contact event durations.</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BCIO:050908</t>
+          <t>BCIO:050509</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1138,23 +1159,23 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>maximum BCI duration</t>
+          <t>mean BCI contact event duration</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>A &lt;BCI duration statistic&gt; that is the highest value from a collection of BCI durations.</t>
+          <t>A &lt;BCI contact event duration statistic&gt; that is the average value calculated from a collection of BCI contact event durations.</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BCIO:050501</t>
+          <t>BCIO:050507</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1165,23 +1186,23 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>minimum BCI duration</t>
+          <t>maximum BCI contact event duration</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>A &lt;BCI duration statistic&gt; that is the lowest value from a collection of BCI durations.</t>
+          <t>A &lt;BCI contact event duration statistic&gt; that is the highest value from a collection of BCI contact event durations.</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BCIO:050498</t>
+          <t>BCIO:050511</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1192,23 +1213,23 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>median BCI duration</t>
+          <t>median BCI contact event duration</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>A &lt;BCI duration statistic&gt; that is the central value of a collection of BCI durations when they are arranged in ascending order.</t>
+          <t>A &lt;BCI contact event duration statistic&gt; that is the central value of a collection of BCI contact event durations when they are arranged in ascending order.</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BCIO:008710</t>
+          <t>BCIO:050516</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1218,33 +1239,24 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>BCI temporal part frequency</t>
+          <t>BCI temporal part frequency statistic</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>A &lt;data item&gt; that is how often intervention temporal parts occur within a BCI.</t>
+          <t>A &lt;data item&gt; that is about a collection of BCI temporal part frequencies.</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>This is useful when grouping contact events together to the schedule of an intervention. For example, authors may describe participants as taking part in 90 minutes of physical activity weekly. These 90 minutes could be split across several contact events, however together these contact events form an intervention part which occurs weekly.; Participants took part in 90 minutes of PA "weekly"</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>How often intervention parts are planned to occur</t>
-        </is>
-      </c>
+      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BCIO:008515</t>
+          <t>BCIO:050517</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1252,35 +1264,26 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>number of BCI contact events</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>maximum BCI temporal part frequency statistic</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>A &lt;data item&gt; that is the number of contact events in a BCI temporal part.</t>
+          <t>A &lt;BCI temporal part frequency statistic&gt; that is the highest value from a collection of BCI temporal part frequencies.</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>one; 6; 12; twenty</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>The planned total number of sessions or digital contacts in an intervention or part</t>
-        </is>
-      </c>
+      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BCIO:050904</t>
+          <t>BCIO:050520</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1288,26 +1291,26 @@
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>BCI contact event number statistic</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>minimum BCI temporal part frequency statistic</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>A &lt;data item&gt; that is about a collection of BCI contact event numbers.</t>
+          <t>A &lt;BCI temporal part frequency statistic&gt; that is the lowest value from a collection of BCI temporal part frequencies.</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BCIO:050912</t>
+          <t>BCIO:050519</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1318,23 +1321,23 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>mean BCI contact event number</t>
+          <t>median BCI temporal part frequency statistic</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>A &lt;BCI contact event number statistic&gt; that is the average value calculated from a collection of BCI contact event numbers.</t>
+          <t>A &lt;BCI temporal part frequency statistic&gt; that is the central value of a collection of BCI temporal part frequencies when they are arranged in ascending order.</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BCIO:050502</t>
+          <t>BCIO:050518</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1345,23 +1348,23 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>minimum BCI contact event number</t>
+          <t>mean BCI temporal part frequency statistic</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>A &lt;BCI contact event number statistic&gt; that is the lowest value from a collection of BCI contact event numbers.</t>
+          <t>A &lt;BCI temporal part frequency statistic&gt; that is the average value calculated from a collection of BCI temporal part frequencies.</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BCIO:050907</t>
+          <t>BCIO:050903</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1369,26 +1372,26 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>maximum BCI contact event number</t>
-        </is>
-      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>BCI contact event frequency statistic</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>A &lt;BCI contact event number statistic&gt; that is the highest value from a collection of BCI contact event numbers.</t>
+          <t>A &lt;data item&gt; that is about a collection of BCI contact event frequencies.</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BCIO:050497</t>
+          <t>BCIO:050911</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1399,23 +1402,23 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>median BCI contact event number</t>
+          <t>mean BCI contact event frequency</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>A &lt;BCI contact event number statistic&gt; that is the central value of a collection of  BCI contact event numbers when they are arranged in ascending order.</t>
+          <t>A &lt;BCI contact event frequency statistic&gt; that is the average value calculated from a collection of BCI contact event frequencies.</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BCIO:050903</t>
+          <t>BCIO:050496</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1423,26 +1426,26 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>BCI contact event frequency statistic</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>median BCI contact event frequency</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>A &lt;data item&gt; that is about a collection of BCI contact event frequencies.</t>
+          <t>A &lt;BCI contact event frequency statistic&gt; that is the central value of a collection of  BCI contact event frequencies when they are arranged in ascending order.</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BCIO:050500</t>
+          <t>BCIO:050906</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1453,23 +1456,23 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>minimum BCI contact event frequency</t>
+          <t>maximum BCI contact event frequency</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>A &lt;BCI contact event frequency statistic&gt; that is the lowest value from a collection of BCI contact event frequencies.</t>
+          <t>A &lt;BCI contact event frequency statistic&gt; that is the highest value from a collection of BCI contact event frequencies.</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BCIO:050906</t>
+          <t>BCIO:050500</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1480,23 +1483,23 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>maximum BCI contact event frequency</t>
+          <t>minimum BCI contact event frequency</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>A &lt;BCI contact event frequency statistic&gt; that is the highest value from a collection of BCI contact event frequencies.</t>
+          <t>A &lt;BCI contact event frequency statistic&gt; that is the lowest value from a collection of BCI contact event frequencies.</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BCIO:050911</t>
+          <t>BCIO:050904</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1504,26 +1507,26 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>mean BCI contact event frequency</t>
-        </is>
-      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>BCI contact event number statistic</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>A &lt;BCI contact event frequency statistic&gt; that is the average value calculated from a collection of BCI contact event frequencies.</t>
+          <t>A &lt;data item&gt; that is about a collection of BCI contact event numbers.</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BCIO:050496</t>
+          <t>BCIO:050907</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1534,23 +1537,23 @@
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>median BCI contact event frequency</t>
+          <t>maximum BCI contact event number</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>A &lt;BCI contact event frequency statistic&gt; that is the central value of a collection of  BCI contact event frequencies when they are arranged in ascending order.</t>
+          <t>A &lt;BCI contact event number statistic&gt; that is the highest value from a collection of BCI contact event numbers.</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BCIO:050505</t>
+          <t>BCIO:050497</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1558,26 +1561,26 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>BCI contact event duration statistic</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>median BCI contact event number</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>A &lt;data item&gt; that is about a collection of BCI contact event durations.</t>
+          <t>A &lt;BCI contact event number statistic&gt; that is the central value of a collection of  BCI contact event numbers when they are arranged in ascending order.</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BCIO:050513</t>
+          <t>BCIO:050912</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1588,23 +1591,23 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>minimum BCI contact event duration</t>
+          <t>mean BCI contact event number</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>A &lt;BCI contact event duration statistic&gt; that is the lowest value from a collection of BCI contact event durations.</t>
+          <t>A &lt;BCI contact event number statistic&gt; that is the average value calculated from a collection of BCI contact event numbers.</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BCIO:050511</t>
+          <t>BCIO:050502</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1615,23 +1618,23 @@
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>median BCI contact event duration</t>
+          <t>minimum BCI contact event number</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>A &lt;BCI contact event duration statistic&gt; that is the central value of a collection of BCI contact event durations when they are arranged in ascending order.</t>
+          <t>A &lt;BCI contact event number statistic&gt; that is the lowest value from a collection of BCI contact event numbers.</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BCIO:050509</t>
+          <t>BCIO:008700</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1639,84 +1642,81 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>mean BCI contact event duration</t>
-        </is>
-      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>BCI contact event frequency</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>A &lt;BCI contact event duration statistic&gt; that is the average value calculated from a collection of BCI contact event durations.</t>
+          <t>A &lt;data item&gt; about the number times a contact event occurs per unit of time.</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>How often intervention sessions or digital contacts are planned to occur</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>twice a week; daily; one a week</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BCIO:050507</t>
+          <t>BFO:0000020</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>specifically dependent continuant</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>maximum BCI contact event duration</t>
-        </is>
-      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>A &lt;BCI contact event duration statistic&gt; that is the highest value from a collection of BCI contact event durations.</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+          <t>A continuant that inheres in or is borne by other entities. Every instance of A requires some specific instance of B which must always be the same.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BCIO:008700</t>
+          <t>PATO:0000044</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>BCI contact event frequency</t>
-        </is>
-      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>A &lt;data item&gt; about the number times a contact event occurs per unit of time.</t>
+          <t>A physical quality which inheres in a bearer by virtue of the number of the bearer's repetitive actions in a particular time.</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>twice a week; daily; one a week</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>How often intervention sessions or digital contacts are planned to occur</t>
-        </is>
-      </c>
+      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1745,14 +1745,14 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BFO:0000008</t>
+          <t>BFO:0000015</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>temporal region</t>
+          <t>process</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -1760,11 +1760,16 @@
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>p is a process = Def. p is an occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t. (axiom label in BFO2 Reference: [083-003])</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BCIO:008530</t>
+          <t>OBI:0000011</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -1772,7 +1777,7 @@
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>temporal reference associated with the intervention</t>
+          <t>planned process</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -1781,85 +1786,65 @@
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>A &lt;temporal region&gt; against which a BCI  temporal part is referenced.</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>Temporal references are used by authors when there is a behaviourally relevant event which structures the schedule of a BCI. This can include things like quit dates, childbirth, medical operations etc.
-We often refer to timepoints when we mean a specific time or some extended period (e.g., Monday). This class allows for the natural usage of a term while maintaining ontological coherence.; A feedback call was scheduled to be delivered around 6 months after the birth of the baby; The smoking intervention started 2 weeks after participants were enrolled into an inpatient setting</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>A statement which describes how the delivery of intervention parts is scheduled relative to associated external events.</t>
+          <t>A process that realizes a plan which is the concretization of a plan specification.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BFO:0000038</t>
+          <t>BCIO:037000</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>one-dimensional temporal region</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>intervention</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>A one-dimensional temporal region is a temporal region that is extended.</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+          <t>A planned process that has the aim of influencing an outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BCIO:008525</t>
+          <t>BCIO:003000</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>BCI contact event duration</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>behaviour change intervention</t>
+        </is>
+      </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>A &lt;temporal interval&gt; between the start and end of a BCI contact event.</t>
+          <t>An intervention that has the aim of influencing human behaviour.</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>1 hour; 30 minutes; 2 minutes</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BCIO:008575</t>
+          <t>BCIO:008505</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -1868,7 +1853,7 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>interval between BCI temporal parts</t>
+          <t>BCI temporal part</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -1876,98 +1861,81 @@
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>A &lt;temporal interval&gt; between the end of one BCI temporal part and the beginning of a subsequent BCI temporal part.</t>
+          <t>A &lt;planned process&gt; that is a part of a BCI.</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>A planned part of an intervention</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>"2 weeks"; "1 day"</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>The planned duration of a break between two parts of an intervention</t>
-        </is>
-      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Temporal parts are defined by the authors of reports. They usually group contact events with similar delivery (e.g. face-to-face), content (e.g. CBT), or contextual features (e.g. school lessons), in order to describe their schedule.; counselling sessions; the first 6 weeks of the intervention; group discussion; a presentation; the last 4 weeks of the intervention</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BCIO:008560</t>
+          <t>BCIO:008510</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>BCI duration</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>BCI contact event</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>A &lt;temporal interval&gt; between the start and end of a BCI.</t>
+          <t>A &lt;BCI temporal part&gt; that is an occasion in which a member of a BCI population comes into contact with a BCI.</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>6 weeks; 2 months; 1 year</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>The planned duration of an intervention</t>
-        </is>
-      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>All contact events are temporal parts, but not all temporal parts are contact events. Whilst contact events are single continuous events, temporal parts of an intervention can  group together multiple different contact events which might have similar features. For example, a set of 10 counselling sessions might be a temporal part within an intervention. The same intervention can have a set of 5 exercise sessions. These 5 sessions together make up another temporal part. Each single session within these parts  is a contact event.; A counselling session; An online chat session; An advertisement display.</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BCIO:008565</t>
+          <t>BFO:0000144</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>BCI temporal part duration</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>process profile</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>A &lt;temporal interval&gt; between the start and end of an intervention temporal part.</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>6 weeks; 2 weeks</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>The planned duration of a part of an intervention</t>
+          <t>b is a process_profile =Def. there is some process c such that b process_profile_of c (axiom label in BFO2 Reference: [093-002])</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BCIO:008545</t>
+          <t>BCIO:043000</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -1976,7 +1944,7 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>total BCI contact event duration</t>
+          <t>process attribute</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -1984,98 +1952,105 @@
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>A &lt;temporal interval&gt; that is the total of intervention temporal parts within a behaviour change intervention.</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>150 minutes; 12 hours</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>The planned total duration of all sessions or digital contacts in an intervention or part</t>
+          <t>A process profile that is an attribute of a process.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BFO:0000015</t>
+          <t>BCIO:050315</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>process</t>
-        </is>
-      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>BCI attribute</t>
+        </is>
+      </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>p is a process = Def. p is an occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t. (axiom label in BFO2 Reference: [083-003])</t>
+          <t>A process attribute whose bearer is a behaviour change intervention.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BFO:0000144</t>
+          <t>BCIO:008500</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>process profile</t>
-        </is>
-      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>BCI schedule of delivery</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>b is a process_profile =Def. there is some process c such that b process_profile_of c (axiom label in BFO2 Reference: [093-002])</t>
-        </is>
-      </c>
+          <t>A &lt;BCI attribute&gt; that is its temporal organisation</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Includes the start and end of a BCI, its parts, and their organisation around relevant timepoints.</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BCIO:043000</t>
+          <t>BCIO:008540</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>process attribute</t>
-        </is>
-      </c>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>irregular intervention schedule</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>A process profile that is an attribute of a process.</t>
-        </is>
-      </c>
+          <t>A &lt;BCI schedule of delivery&gt; in which the frequency and duration of contact events change over the course of a temporal part or BCI.</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>A type of schedule which plans that the duration and frequency of sessions or digital contacts vary across the course of an intervention</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>telephone feedback sessions were more frequent during the first 6 weeks; participants were free to access the app whenever they desired</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BCIO:050315</t>
+          <t>BCIO:008535</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2083,23 +2058,35 @@
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>BCI attribute</t>
-        </is>
-      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>regular intervention schedule</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>A process attribute whose bearer is a behaviour change intervention.</t>
-        </is>
-      </c>
+          <t>A &lt;BCI schedule of delivery&gt; in which the frequency and duration of Intervention temporal parts are uniform across the course of a BCI or BCI part.</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>A type of schedule which plans that the duration and frequency of sessions or digital contacts remain constant across the course of an intervention</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>the length and regularity of sessions were consistent across the duration of the intervention, taking place for an hour each week</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BCIO:008500</t>
+          <t>BCIO:008580</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2110,120 +2097,17 @@
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>BCI schedule of delivery</t>
+          <t>order of BCI temporal parts</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>A &lt;BCI attribute&gt; that is its temporal organisation</t>
+          <t>A &lt;BCI attribute&gt; that is the  temporal positioning of BCI temporal parts.</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>Includes the start and end of a BCI, its parts, and their organisation around relevant timepoints.</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>BCIO:008535</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr"/>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>regular intervention schedule</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>A &lt;BCI schedule of delivery&gt; in which the frequency and duration of Intervention temporal parts are uniform across the course of a BCI or BCI part.</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>the length and regularity of sessions were consistent across the duration of the intervention, taking place for an hour each week</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>A type of schedule which plans that the duration and frequency of sessions or digital contacts remain constant across the course of an intervention</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>BCIO:008540</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr"/>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>irregular intervention schedule</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>A &lt;BCI schedule of delivery&gt; in which the frequency and duration of contact events change over the course of a temporal part or BCI.</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>telephone feedback sessions were more frequent during the first 6 weeks; participants were free to access the app whenever they desired</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>A type of schedule which plans that the duration and frequency of sessions or digital contacts vary across the course of an intervention</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>BCIO:008580</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>order of BCI temporal parts</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>A &lt;BCI attribute&gt; that is the  temporal positioning of BCI temporal parts.</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>"After questionnaires were completed, feedback was selected
 out of a database with messages for each possible combination
@@ -2232,36 +2116,131 @@
 levels to the PA guidelines."</t>
         </is>
       </c>
+      <c r="O61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>BFO:0000008</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>temporal region</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>BCIO:008530</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>temporal reference associated with the intervention</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>A &lt;temporal region&gt; against which a BCI  temporal part is referenced.</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>A statement which describes how the delivery of intervention parts is scheduled relative to associated external events.</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Temporal references are used by authors when there is a behaviourally relevant event which structures the schedule of a BCI. This can include things like quit dates, childbirth, medical operations etc.
+We often refer to timepoints when we mean a specific time or some extended period (e.g., Monday). This class allows for the natural usage of a term while maintaining ontological coherence.; A feedback call was scheduled to be delivered around 6 months after the birth of the baby; The smoking intervention started 2 weeks after participants were enrolled into an inpatient setting</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>BFO:0000038</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>temporal interval</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region is a temporal region that is extended.</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>OBI:0000011</t>
+          <t>BCIO:008575</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>planned process</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>interval between BCI temporal parts</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
-          <t>A process that realizes a plan which is the concretization of a plan specification.</t>
-        </is>
-      </c>
+          <t>A &lt;temporal interval&gt; between the end of one BCI temporal part and the beginning of a subsequent BCI temporal part.</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>The planned duration of a break between two parts of an intervention</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>"2 weeks"; "1 day"</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BCIO:008505</t>
+          <t>BCIO:008565</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -2270,7 +2249,7 @@
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>BCI temporal part</t>
+          <t>BCI temporal part duration</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -2278,57 +2257,62 @@
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
-          <t>A &lt;planned process&gt; that is a part of a BCI.</t>
+          <t>A &lt;temporal interval&gt; between the start and end of an intervention temporal part.</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>The planned duration of a part of an intervention</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>Temporal parts are defined by the authors of reports. They usually group contact events with similar delivery (e.g. face-to-face), content (e.g. CBT), or contextual features (e.g. school lessons), in order to describe their schedule.; counselling sessions; the first 6 weeks of the intervention; group discussion; a presentation; the last 4 weeks of the intervention</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>A planned part of an intervention</t>
-        </is>
-      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>6 weeks; 2 weeks</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BCIO:008510</t>
+          <t>BCIO:008560</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>BCI contact event</t>
-        </is>
-      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>BCI duration</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
-          <t>A &lt;BCI temporal part&gt; that is an occasion in which a member of a BCI population comes into contact with a BCI.</t>
+          <t>A &lt;temporal interval&gt; between the start and end of a BCI.</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>The planned duration of an intervention</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>All contact events are temporal parts, but not all temporal parts are contact events. Whilst contact events are single continuous events, temporal parts of an intervention can  group together multiple different contact events which might have similar features. For example, a set of 10 counselling sessions might be a temporal part within an intervention. The same intervention can have a set of 5 exercise sessions. These 5 sessions together make up another temporal part. Each single session within these parts  is a contact event.; A counselling session; An online chat session; An advertisement display.</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>6 weeks; 2 months; 1 year</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BCIO:037000</t>
+          <t>BCIO:008545</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -2337,7 +2321,7 @@
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>intervention</t>
+          <t>total BCI contact event duration</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -2345,36 +2329,52 @@
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>A planned process that has the aim of influencing an outcome.</t>
-        </is>
-      </c>
+          <t>A &lt;temporal interval&gt; that is the total of intervention temporal parts within a behaviour change intervention.</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>The planned total duration of all sessions or digital contacts in an intervention or part</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>150 minutes; 12 hours</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BCIO:003000</t>
+          <t>BCIO:008525</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>behaviour change intervention</t>
-        </is>
-      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>BCI contact event duration</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>An intervention that has the aim of influencing human behaviour.</t>
+          <t>A &lt;temporal interval&gt; between the start and end of a BCI contact event.</t>
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>1 hour; 30 minutes; 2 minutes</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Schedule/BCIO-schedule-hierarchy.xlsx
+++ b/Schedule/BCIO-schedule-hierarchy.xlsx
@@ -441,32 +441,32 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>synonyms</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>subontology</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>crossreference</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>examples</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>informaldefinition</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>synonyms</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>comment</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>examples</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>crossreference</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>subontology</t>
         </is>
       </c>
     </row>
@@ -521,13 +521,13 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BFO:0000002</t>
+          <t>BFO:0000003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>continuant</t>
+          <t>occurrent</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,21 +538,21 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>An entity that exists in full at any time in which it exists at all, persists through time while maintaining its identity and has no temporal parts.</t>
+          <t>An entity that has temporal parts and that happens, unfolds or develops through time.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BFO:0000031</t>
+          <t>BFO:0000015</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>generically dependent continuant</t>
+          <t>process</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -562,14 +562,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>b is a generically dependent continuant = Def. b is a continuant that g-depends_on one or more other entities. (axiom label in BFO2 Reference: [074-001])</t>
+          <t>An occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IAO:0000030</t>
+          <t>BFO:0000144</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -577,7 +577,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>information content entity</t>
+          <t>process profile</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -586,14 +586,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>A generically dependent continuant that is about some thing.</t>
+          <t>b is a process_profile =Def. there is some process c such that b process_profile_of c (axiom label in BFO2 Reference: [093-002])</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IAO:0000027</t>
+          <t>BCIO:043000</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -602,7 +602,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>data item</t>
+          <t>process attribute</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -610,14 +610,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>An information content entity that is intended to be a truthful statement about something (modulo, e.g., measurement precision or other systematic errors) and is constructed/acquired by a method which reliably tends to produce (approximately) truthful statements.</t>
+          <t>A process profile that is an attribute of a process.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BCIO:008710</t>
+          <t>BCIO:050315</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -627,33 +627,21 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>BCI temporal part frequency</t>
+          <t>BCI attribute</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>A &lt;data item&gt; that is how often intervention temporal parts occur within a BCI.</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>How often intervention parts are planned to occur</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>This is useful when grouping contact events together to the schedule of an intervention. For example, authors may describe participants as taking part in 90 minutes of physical activity weekly. These 90 minutes could be split across several contact events, however together these contact events form an intervention part which occurs weekly.; Participants took part in 90 minutes of PA "weekly"</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
+          <t>A process attribute whose bearer is a behaviour change intervention.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BCIO:008515</t>
+          <t>BCIO:008580</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -661,35 +649,34 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>number of BCI contact events</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>order of BCI temporal parts</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>A &lt;data item&gt; that is the number of contact events in a BCI temporal part.</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>The planned total number of sessions or digital contacts in an intervention or part</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>A &lt;BCI attribute&gt; that is the  temporal positioning of BCI temporal parts.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>one; 6; 12; twenty</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
+          <t>"After questionnaires were completed, feedback was selected
+out of a database with messages for each possible combination
+of answers."; "The PA advice started with a general introduction,
+followed by normative feedback, which related students’ PA
+levels to the PA guidelines."</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BCIO:050905</t>
+          <t>BCIO:008500</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -697,26 +684,30 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>BCI duration statistic</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>BCI schedule of delivery</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>A &lt;data item&gt; that is about a collection of BCI durations.</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+          <t>A &lt;BCI attribute&gt; that is its temporal organisation</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Includes the start and end of a BCI, its parts, and their organisation around relevant timepoints.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BCIO:050908</t>
+          <t>BCIO:008535</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -725,25 +716,34 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>maximum BCI duration</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>regular intervention schedule</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>A &lt;BCI duration statistic&gt; that is the highest value from a collection of BCI durations.</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+          <t>A &lt;BCI schedule of delivery&gt; in which the frequency and duration of Intervention temporal parts are uniform across the course of a BCI or BCI part.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>the length and regularity of sessions were consistent across the duration of the intervention, taking place for an hour each week</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>A type of schedule which plans that the duration and frequency of sessions or digital contacts remain constant across the course of an intervention</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BCIO:050909</t>
+          <t>BCIO:008540</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -752,79 +752,82 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>mean BCI duration</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>irregular intervention schedule</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>A &lt;BCI duration statistic&gt; that is the average value calculated from a collection of BCI durations.</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+          <t>A &lt;BCI schedule of delivery&gt; in which the frequency and duration of contact events change over the course of a temporal part or BCI.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>telephone feedback sessions were more frequent during the first 6 weeks; participants were free to access the app whenever they desired</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>A type of schedule which plans that the duration and frequency of sessions or digital contacts vary across the course of an intervention</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BCIO:050501</t>
+          <t>OBI:0000011</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>planned process</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>minimum BCI duration</t>
-        </is>
-      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>A &lt;BCI duration statistic&gt; that is the lowest value from a collection of BCI durations.</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+          <t>A process that realizes a plan which is the concretization of a plan specification.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BCIO:050498</t>
+          <t>BCIO:037000</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>intervention</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>median BCI duration</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>A &lt;BCI duration statistic&gt; that is the central value of a collection of BCI durations when they are arranged in ascending order.</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+          <t>A planned process that has the aim of influencing an outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCIO:050504</t>
+          <t>BCIO:003000</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -834,51 +837,60 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>total BCI contact event duration statistic</t>
+          <t>behaviour change intervention</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>A &lt;data item&gt; that is about a collection of total contact event durations.</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+          <t>An intervention that has the aim of influencing human behaviour.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BCIO:050499</t>
+          <t>BCIO:008505</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>BCI temporal part</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>median total BCI contact event duration</t>
-        </is>
-      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>A &lt;total contact event duration statistic&gt; that is the central value of a collection of total contact event durations when they are arranged in ascending order.</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+          <t>A &lt;planned process&gt; that is a part of a BCI.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Temporal parts are defined by the authors of reports. They usually group contact events with similar delivery (e.g. face-to-face), content (e.g. CBT), or contextual features (e.g. school lessons), in order to describe their schedule.; counselling sessions; the first 6 weeks of the intervention; group discussion; a presentation; the last 4 weeks of the intervention</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>A planned part of an intervention</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BCIO:050910</t>
+          <t>BCIO:008510</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -886,404 +898,435 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>maximum total BCI contact event duration</t>
-        </is>
-      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>BCI contact event</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>A &lt;total contact event duration statistic&gt; that is the highest value from a collection of total contact event durations.</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+          <t>A &lt;BCI temporal part&gt; that is an occasion in which a member of a BCI population comes into contact with a BCI.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>All contact events are temporal parts, but not all temporal parts are contact events. Whilst contact events are single continuous events, temporal parts of an intervention can  group together multiple different contact events which might have similar features. For example, a set of 10 counselling sessions might be a temporal part within an intervention. The same intervention can have a set of 5 exercise sessions. These 5 sessions together make up another temporal part. Each single session within these parts  is a contact event.; A counselling session; An online chat session; An advertisement display.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BCIO:050495</t>
+          <t>BFO:0000008</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>temporal region</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>mean total BCI contact event duration</t>
-        </is>
-      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>A &lt;total contact event duration statistic&gt; that is the average value calculated from a collection of total contact event durations.</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BCIO:050503</t>
+          <t>BFO:0000038</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>one-dimensional temporal region</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>minimum total BCI contact event duration</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>A &lt;total contact event duration statistic&gt; that is the lowest value from a collection of total contact event durations.</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+          <t>A one-dimensional temporal region is a temporal region that is extended.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BCIO:050506</t>
+          <t>BCIO:008575</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>BCI temporal part duration statistic</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>interval between BCI temporal parts</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>A &lt;data item&gt; that is about a collection of intervention temporal part durations.</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+          <t>A &lt;temporal interval&gt; between the end of one BCI temporal part and the beginning of a subsequent BCI temporal part.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>"2 weeks"; "1 day"</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>The planned duration of a break between two parts of an intervention</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BCIO:050508</t>
+          <t>BCIO:008525</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>BCI contact event duration</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>maximum BCI temporal part duration</t>
-        </is>
-      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>A &lt;BCI temporal part duration statistic&gt; that denotes the highest value from a collection of BCI temporal part durations.</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
+          <t>A &lt;temporal interval&gt; between the start and end of a BCI contact event.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>1 hour; 30 minutes; 2 minutes</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BCIO:050514</t>
+          <t>BCIO:008545</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>total BCI contact event duration</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>minimum BCI temporal part duration</t>
-        </is>
-      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>A &lt;BCI temporal part duration statistic&gt; that denotes the lowest value from a collection of BCI temporal part durations.</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
+          <t>A &lt;temporal interval&gt; that is the total of intervention temporal parts within a behaviour change intervention.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>150 minutes; 12 hours</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>The planned total duration of all sessions or digital contacts in an intervention or part</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BCIO:050512</t>
+          <t>BCIO:008560</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>BCI duration</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>median BCI temporal part duration</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>A &lt;BCI temporal part duration statistic&gt; that is the central value of a collection of BCI temporal part durations when they are arranged in ascending order.</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
+          <t>A &lt;temporal interval&gt; between the start and end of a BCI.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>6 weeks; 2 months; 1 year</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>The planned duration of an intervention</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BCIO:050510</t>
+          <t>BCIO:008565</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>BCI temporal part duration</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>mean BCI temporal part duration</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>A &lt;BCI temporal part duration statistic&gt; that is the average value calculated from a collection of BCI temporal part durations.</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
+          <t>A &lt;temporal interval&gt; between the start and end of an intervention temporal part.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>6 weeks; 2 weeks</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>The planned duration of a part of an intervention</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BCIO:050505</t>
+          <t>BCIO:008530</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>temporal reference associated with the intervention</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>BCI contact event duration statistic</t>
-        </is>
-      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>A &lt;data item&gt; that is about a collection of BCI contact event durations.</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+          <t>A &lt;temporal region&gt; against which a BCI  temporal part is referenced.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Temporal references are used by authors when there is a behaviourally relevant event which structures the schedule of a BCI. This can include things like quit dates, childbirth, medical operations etc.
+We often refer to timepoints when we mean a specific time or some extended period (e.g., Monday). This class allows for the natural usage of a term while maintaining ontological coherence.; A feedback call was scheduled to be delivered around 6 months after the birth of the baby; The smoking intervention started 2 weeks after participants were enrolled into an inpatient setting</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>A statement which describes how the delivery of intervention parts is scheduled relative to associated external events.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BCIO:050513</t>
+          <t>BFO:0000002</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>continuant</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>minimum BCI contact event duration</t>
-        </is>
-      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>A &lt;BCI contact event duration statistic&gt; that is the lowest value from a collection of BCI contact event durations.</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+          <t>An entity that exists in full at any time in which it exists at all, persists through time while maintaining its identity and has no temporal parts.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BCIO:050509</t>
+          <t>BFO:0000020</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>characteristic</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>mean BCI contact event duration</t>
-        </is>
-      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>A &lt;BCI contact event duration statistic&gt; that is the average value calculated from a collection of BCI contact event durations.</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
+          <t>b is a specifically dependent continuant = Def. b is a continuant &amp; there is some independent continuant c which is not a spatial region and which is such that b s-depends_on c at every time t during the course of b’s existence. (axiom label in BFO2 Reference: [050-003])</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BCIO:050507</t>
+          <t>PATO:0000044</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>maximum BCI contact event duration</t>
-        </is>
-      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>A &lt;BCI contact event duration statistic&gt; that is the highest value from a collection of BCI contact event durations.</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
+          <t>A physical quality which inheres in a bearer by virtue of the number of the bearer's repetitive actions in a particular time.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BCIO:050511</t>
+          <t>BFO:0000031</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>generically dependent continuant</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>median BCI contact event duration</t>
-        </is>
-      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>A &lt;BCI contact event duration statistic&gt; that is the central value of a collection of BCI contact event durations when they are arranged in ascending order.</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
+          <t>b is a generically dependent continuant = Def. b is a continuant that g-depends_on one or more other entities. (axiom label in BFO2 Reference: [074-001])</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BCIO:050516</t>
+          <t>IAO:0000030</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>information content entity</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>BCI temporal part frequency statistic</t>
-        </is>
-      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>A &lt;data item&gt; that is about a collection of BCI temporal part frequencies.</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
+          <t>A generically dependent continuant that is about some thing.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BCIO:050517</t>
+          <t>IAO:0000027</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>data item</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>maximum BCI temporal part frequency statistic</t>
-        </is>
-      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>A &lt;BCI temporal part frequency statistic&gt; that is the highest value from a collection of BCI temporal part frequencies.</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
+          <t>An information content entity that is intended to be a truthful statement about something (modulo, e.g., measurement precision or other systematic errors) and is constructed/acquired by a method which reliably tends to produce (approximately) truthful statements.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BCIO:050520</t>
+          <t>BCIO:050504</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1291,26 +1334,26 @@
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>minimum BCI temporal part frequency statistic</t>
-        </is>
-      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>total BCI contact event duration statistic</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>A &lt;BCI temporal part frequency statistic&gt; that is the lowest value from a collection of BCI temporal part frequencies.</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
+          <t>A &lt;data item&gt; that is about a collection of total contact event durations.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BCIO:050519</t>
+          <t>BCIO:050910</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1321,23 +1364,23 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>median BCI temporal part frequency statistic</t>
+          <t>maximum total BCI contact event duration</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>A &lt;BCI temporal part frequency statistic&gt; that is the central value of a collection of BCI temporal part frequencies when they are arranged in ascending order.</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
+          <t>A &lt;total contact event duration statistic&gt; that is the highest value from a collection of total contact event durations.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BCIO:050518</t>
+          <t>BCIO:050503</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1348,23 +1391,23 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>mean BCI temporal part frequency statistic</t>
+          <t>minimum total BCI contact event duration</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>A &lt;BCI temporal part frequency statistic&gt; that is the average value calculated from a collection of BCI temporal part frequencies.</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
+          <t>A &lt;total contact event duration statistic&gt; that is the lowest value from a collection of total contact event durations.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BCIO:050903</t>
+          <t>BCIO:050495</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1372,26 +1415,26 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>BCI contact event frequency statistic</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>mean total BCI contact event duration</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>A &lt;data item&gt; that is about a collection of BCI contact event frequencies.</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
+          <t>A &lt;total contact event duration statistic&gt; that is the average value calculated from a collection of total contact event durations.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BCIO:050911</t>
+          <t>BCIO:050499</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1402,23 +1445,23 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>mean BCI contact event frequency</t>
+          <t>median total BCI contact event duration</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>A &lt;BCI contact event frequency statistic&gt; that is the average value calculated from a collection of BCI contact event frequencies.</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
+          <t>A &lt;total contact event duration statistic&gt; that is the central value of a collection of total contact event durations when they are arranged in ascending order.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BCIO:050496</t>
+          <t>BCIO:008700</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1426,26 +1469,35 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>median BCI contact event frequency</t>
-        </is>
-      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>BCI contact event frequency</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>A &lt;BCI contact event frequency statistic&gt; that is the central value of a collection of  BCI contact event frequencies when they are arranged in ascending order.</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
+          <t>A &lt;data item&gt; about the number times a contact event occurs per unit of time.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>twice a week; daily; one a week</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>How often intervention sessions or digital contacts are planned to occur</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BCIO:050906</t>
+          <t>BCIO:050516</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1453,26 +1505,26 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>maximum BCI contact event frequency</t>
-        </is>
-      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>BCI temporal part frequency statistic</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>A &lt;BCI contact event frequency statistic&gt; that is the highest value from a collection of BCI contact event frequencies.</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr"/>
+          <t>A &lt;data item&gt; that is about a collection of BCI temporal part frequencies.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BCIO:050500</t>
+          <t>BCIO:050517</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1483,23 +1535,23 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>minimum BCI contact event frequency</t>
+          <t>maximum BCI temporal part frequency statistic</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>A &lt;BCI contact event frequency statistic&gt; that is the lowest value from a collection of BCI contact event frequencies.</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
+          <t>A &lt;BCI temporal part frequency statistic&gt; that is the highest value from a collection of BCI temporal part frequencies.</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BCIO:050904</t>
+          <t>BCIO:050520</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1507,26 +1559,26 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>BCI contact event number statistic</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>minimum BCI temporal part frequency statistic</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>A &lt;data item&gt; that is about a collection of BCI contact event numbers.</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr"/>
+          <t>A &lt;BCI temporal part frequency statistic&gt; that is the lowest value from a collection of BCI temporal part frequencies.</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BCIO:050907</t>
+          <t>BCIO:050518</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1537,23 +1589,23 @@
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>maximum BCI contact event number</t>
+          <t>mean BCI temporal part frequency statistic</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>A &lt;BCI contact event number statistic&gt; that is the highest value from a collection of BCI contact event numbers.</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr"/>
+          <t>A &lt;BCI temporal part frequency statistic&gt; that is the average value calculated from a collection of BCI temporal part frequencies.</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BCIO:050497</t>
+          <t>BCIO:050519</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1564,23 +1616,23 @@
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>median BCI contact event number</t>
+          <t>median BCI temporal part frequency statistic</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>A &lt;BCI contact event number statistic&gt; that is the central value of a collection of  BCI contact event numbers when they are arranged in ascending order.</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr"/>
+          <t>A &lt;BCI temporal part frequency statistic&gt; that is the central value of a collection of BCI temporal part frequencies when they are arranged in ascending order.</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BCIO:050912</t>
+          <t>BCIO:050505</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1588,26 +1640,26 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>mean BCI contact event number</t>
-        </is>
-      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>BCI contact event duration statistic</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>A &lt;BCI contact event number statistic&gt; that is the average value calculated from a collection of BCI contact event numbers.</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr"/>
+          <t>A &lt;data item&gt; that is about a collection of BCI contact event durations.</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BCIO:050502</t>
+          <t>BCIO:050513</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1618,23 +1670,23 @@
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>minimum BCI contact event number</t>
+          <t>minimum BCI contact event duration</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>A &lt;BCI contact event number statistic&gt; that is the lowest value from a collection of BCI contact event numbers.</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
+          <t>A &lt;BCI contact event duration statistic&gt; that is the lowest value from a collection of BCI contact event durations.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BCIO:008700</t>
+          <t>BCIO:050509</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1642,182 +1694,188 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>BCI contact event frequency</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>mean BCI contact event duration</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>A &lt;data item&gt; about the number times a contact event occurs per unit of time.</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>How often intervention sessions or digital contacts are planned to occur</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>twice a week; daily; one a week</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr"/>
+          <t>A &lt;BCI contact event duration statistic&gt; that is the average value calculated from a collection of BCI contact event durations.</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BFO:0000020</t>
+          <t>BCIO:050511</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>specifically dependent continuant</t>
-        </is>
-      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>median BCI contact event duration</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>A continuant that inheres in or is borne by other entities. Every instance of A requires some specific instance of B which must always be the same.</t>
-        </is>
-      </c>
+          <t>A &lt;BCI contact event duration statistic&gt; that is the central value of a collection of BCI contact event durations when they are arranged in ascending order.</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PATO:0000044</t>
+          <t>BCIO:050507</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>frequency</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>maximum BCI contact event duration</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>A physical quality which inheres in a bearer by virtue of the number of the bearer's repetitive actions in a particular time.</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr"/>
+          <t>A &lt;BCI contact event duration statistic&gt; that is the highest value from a collection of BCI contact event durations.</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BFO:0000003</t>
+          <t>BCIO:050506</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>occurrent</t>
-        </is>
-      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>BCI temporal part duration statistic</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>An entity that has temporal parts and that happens, unfolds or develops through time.</t>
-        </is>
-      </c>
+          <t>A &lt;data item&gt; that is about a collection of intervention temporal part durations.</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BFO:0000015</t>
+          <t>BCIO:050514</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>process</t>
-        </is>
-      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>minimum BCI temporal part duration</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>p is a process = Def. p is an occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t. (axiom label in BFO2 Reference: [083-003])</t>
-        </is>
-      </c>
+          <t>A &lt;BCI temporal part duration statistic&gt; that denotes the lowest value from a collection of BCI temporal part durations.</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>OBI:0000011</t>
+          <t>BCIO:050508</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>planned process</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>maximum BCI temporal part duration</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>A process that realizes a plan which is the concretization of a plan specification.</t>
-        </is>
-      </c>
+          <t>A &lt;BCI temporal part duration statistic&gt; that denotes the highest value from a collection of BCI temporal part durations.</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BCIO:037000</t>
+          <t>BCIO:050510</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>intervention</t>
-        </is>
-      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>mean BCI temporal part duration</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>A planned process that has the aim of influencing an outcome.</t>
-        </is>
-      </c>
+          <t>A &lt;BCI temporal part duration statistic&gt; that is the average value calculated from a collection of BCI temporal part durations.</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BCIO:003000</t>
+          <t>BCIO:050512</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -1825,62 +1883,53 @@
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>behaviour change intervention</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>median BCI temporal part duration</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>An intervention that has the aim of influencing human behaviour.</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr"/>
+          <t>A &lt;BCI temporal part duration statistic&gt; that is the central value of a collection of BCI temporal part durations when they are arranged in ascending order.</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BCIO:008505</t>
+          <t>BCIO:050903</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>BCI temporal part</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>BCI contact event frequency statistic</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>A &lt;planned process&gt; that is a part of a BCI.</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>A planned part of an intervention</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>Temporal parts are defined by the authors of reports. They usually group contact events with similar delivery (e.g. face-to-face), content (e.g. CBT), or contextual features (e.g. school lessons), in order to describe their schedule.; counselling sessions; the first 6 weeks of the intervention; group discussion; a presentation; the last 4 weeks of the intervention</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr"/>
+          <t>A &lt;data item&gt; that is about a collection of BCI contact event frequencies.</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BCIO:008510</t>
+          <t>BCIO:050911</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -1888,78 +1937,80 @@
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>BCI contact event</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>mean BCI contact event frequency</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>A &lt;BCI temporal part&gt; that is an occasion in which a member of a BCI population comes into contact with a BCI.</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>All contact events are temporal parts, but not all temporal parts are contact events. Whilst contact events are single continuous events, temporal parts of an intervention can  group together multiple different contact events which might have similar features. For example, a set of 10 counselling sessions might be a temporal part within an intervention. The same intervention can have a set of 5 exercise sessions. These 5 sessions together make up another temporal part. Each single session within these parts  is a contact event.; A counselling session; An online chat session; An advertisement display.</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr"/>
+          <t>A &lt;BCI contact event frequency statistic&gt; that is the average value calculated from a collection of BCI contact event frequencies.</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BFO:0000144</t>
+          <t>BCIO:050496</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>process profile</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>median BCI contact event frequency</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>b is a process_profile =Def. there is some process c such that b process_profile_of c (axiom label in BFO2 Reference: [093-002])</t>
-        </is>
-      </c>
+          <t>A &lt;BCI contact event frequency statistic&gt; that is the central value of a collection of  BCI contact event frequencies when they are arranged in ascending order.</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BCIO:043000</t>
+          <t>BCIO:050500</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>process attribute</t>
-        </is>
-      </c>
+      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>minimum BCI contact event frequency</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>A process profile that is an attribute of a process.</t>
-        </is>
-      </c>
+          <t>A &lt;BCI contact event frequency statistic&gt; that is the lowest value from a collection of BCI contact event frequencies.</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BCIO:050315</t>
+          <t>BCIO:050906</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -1967,23 +2018,26 @@
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>BCI attribute</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>maximum BCI contact event frequency</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>A process attribute whose bearer is a behaviour change intervention.</t>
-        </is>
-      </c>
+          <t>A &lt;BCI contact event frequency statistic&gt; that is the highest value from a collection of BCI contact event frequencies.</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BCIO:008500</t>
+          <t>BCIO:050904</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -1991,30 +2045,26 @@
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>BCI schedule of delivery</t>
-        </is>
-      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>BCI contact event number statistic</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>A &lt;BCI attribute&gt; that is its temporal organisation</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>Includes the start and end of a BCI, its parts, and their organisation around relevant timepoints.</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr"/>
+          <t>A &lt;data item&gt; that is about a collection of BCI contact event numbers.</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BCIO:008540</t>
+          <t>BCIO:050907</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2023,34 +2073,25 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>irregular intervention schedule</t>
-        </is>
-      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>maximum BCI contact event number</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>A &lt;BCI schedule of delivery&gt; in which the frequency and duration of contact events change over the course of a temporal part or BCI.</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>A type of schedule which plans that the duration and frequency of sessions or digital contacts vary across the course of an intervention</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>telephone feedback sessions were more frequent during the first 6 weeks; participants were free to access the app whenever they desired</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr"/>
+          <t>A &lt;BCI contact event number statistic&gt; that is the highest value from a collection of BCI contact event numbers.</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BCIO:008535</t>
+          <t>BCIO:050912</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2059,34 +2100,25 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>regular intervention schedule</t>
-        </is>
-      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>mean BCI contact event number</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>A &lt;BCI schedule of delivery&gt; in which the frequency and duration of Intervention temporal parts are uniform across the course of a BCI or BCI part.</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>A type of schedule which plans that the duration and frequency of sessions or digital contacts remain constant across the course of an intervention</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>the length and regularity of sessions were consistent across the duration of the intervention, taking place for an hour each week</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr"/>
+          <t>A &lt;BCI contact event number statistic&gt; that is the average value calculated from a collection of BCI contact event numbers.</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BCIO:008580</t>
+          <t>BCIO:050502</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2097,284 +2129,252 @@
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>order of BCI temporal parts</t>
+          <t>minimum BCI contact event number</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>A &lt;BCI attribute&gt; that is the  temporal positioning of BCI temporal parts.</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>"After questionnaires were completed, feedback was selected
-out of a database with messages for each possible combination
-of answers."; "The PA advice started with a general introduction,
-followed by normative feedback, which related students’ PA
-levels to the PA guidelines."</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr"/>
+          <t>A &lt;BCI contact event number statistic&gt; that is the lowest value from a collection of BCI contact event numbers.</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BFO:0000008</t>
+          <t>BCIO:050497</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>temporal region</t>
-        </is>
-      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>median BCI contact event number</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>A &lt;BCI contact event number statistic&gt; that is the central value of a collection of  BCI contact event numbers when they are arranged in ascending order.</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BCIO:008530</t>
+          <t>BCIO:008515</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>temporal reference associated with the intervention</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>number of BCI contact events</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>A &lt;temporal region&gt; against which a BCI  temporal part is referenced.</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>A statement which describes how the delivery of intervention parts is scheduled relative to associated external events.</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr"/>
+          <t>A &lt;data item&gt; that is the number of contact events in a BCI temporal part.</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Temporal references are used by authors when there is a behaviourally relevant event which structures the schedule of a BCI. This can include things like quit dates, childbirth, medical operations etc.
-We often refer to timepoints when we mean a specific time or some extended period (e.g., Monday). This class allows for the natural usage of a term while maintaining ontological coherence.; A feedback call was scheduled to be delivered around 6 months after the birth of the baby; The smoking intervention started 2 weeks after participants were enrolled into an inpatient setting</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr"/>
+          <t>one; 6; 12; twenty</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>The planned total number of sessions or digital contacts in an intervention or part</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BFO:0000038</t>
+          <t>BCIO:008710</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>temporal interval</t>
-        </is>
-      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>BCI temporal part frequency</t>
+        </is>
+      </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
-          <t>A one-dimensional temporal region is a temporal region that is extended.</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
+          <t>A &lt;data item&gt; that is how often intervention temporal parts occur within a BCI.</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>This is useful when grouping contact events together to the schedule of an intervention. For example, authors may describe participants as taking part in 90 minutes of physical activity weekly. These 90 minutes could be split across several contact events, however together these contact events form an intervention part which occurs weekly.; Participants took part in 90 minutes of PA "weekly"</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>How often intervention parts are planned to occur</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BCIO:008575</t>
+          <t>BCIO:050905</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>interval between BCI temporal parts</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>BCI duration statistic</t>
+        </is>
+      </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
-          <t>A &lt;temporal interval&gt; between the end of one BCI temporal part and the beginning of a subsequent BCI temporal part.</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>The planned duration of a break between two parts of an intervention</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>"2 weeks"; "1 day"</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr"/>
+          <t>A &lt;data item&gt; that is about a collection of BCI durations.</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BCIO:008565</t>
+          <t>BCIO:050501</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>BCI temporal part duration</t>
-        </is>
-      </c>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>minimum BCI duration</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
-          <t>A &lt;temporal interval&gt; between the start and end of an intervention temporal part.</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>The planned duration of a part of an intervention</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>6 weeks; 2 weeks</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr"/>
+          <t>A &lt;BCI duration statistic&gt; that is the lowest value from a collection of BCI durations.</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BCIO:008560</t>
+          <t>BCIO:050908</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>BCI duration</t>
-        </is>
-      </c>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>maximum BCI duration</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
-          <t>A &lt;temporal interval&gt; between the start and end of a BCI.</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>The planned duration of an intervention</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr"/>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>6 weeks; 2 months; 1 year</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr"/>
+          <t>A &lt;BCI duration statistic&gt; that is the highest value from a collection of BCI durations.</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BCIO:008545</t>
+          <t>BCIO:050498</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>total BCI contact event duration</t>
-        </is>
-      </c>
+      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>median BCI duration</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>A &lt;temporal interval&gt; that is the total of intervention temporal parts within a behaviour change intervention.</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>The planned total duration of all sessions or digital contacts in an intervention or part</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr"/>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>150 minutes; 12 hours</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr"/>
+          <t>A &lt;BCI duration statistic&gt; that is the central value of a collection of BCI durations when they are arranged in ascending order.</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BCIO:008525</t>
+          <t>BCIO:050909</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>BCI contact event duration</t>
-        </is>
-      </c>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>mean BCI duration</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>A &lt;temporal interval&gt; between the start and end of a BCI contact event.</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr"/>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>1 hour; 30 minutes; 2 minutes</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr"/>
+          <t>A &lt;BCI duration statistic&gt; that is the average value calculated from a collection of BCI durations.</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Schedule/BCIO-schedule-hierarchy.xlsx
+++ b/Schedule/BCIO-schedule-hierarchy.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P69"/>
+  <dimension ref="A1:Q85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,37 +434,38 @@
       <c r="G1" t="inlineStr"/>
       <c r="H1" t="inlineStr"/>
       <c r="I1" t="inlineStr"/>
-      <c r="J1" t="inlineStr">
+      <c r="J1" t="inlineStr"/>
+      <c r="K1" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>crossreference</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
         <is>
           <t>synonyms</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>informaldefinition</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>subontology</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>crossreference</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>examples</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>informaldefinition</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
@@ -488,7 +489,8 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
         <is>
           <t>An entity is anything that exists or has existed or will exist.</t>
         </is>
@@ -512,7 +514,8 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
         <is>
           <t>An entity is anything that exists or has existed or will exist.</t>
         </is>
@@ -521,13 +524,13 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BFO:0000003</t>
+          <t>BFO:0000002</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>occurrent</t>
+          <t>continuant</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -536,23 +539,24 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>An entity that has temporal parts and that happens, unfolds or develops through time.</t>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>An entity that exists in full at any time in which it exists at all, persists through time while maintaining its identity and has no temporal parts.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BFO:0000015</t>
+          <t>BFO:0000020</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>specifically dependent continuant</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -560,16 +564,17 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>An occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t.</t>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>A continuant that inheres in or is borne by other entities. Every instance of A requires some specific instance of B which must always be the same.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BFO:0000144</t>
+          <t>PATO:0000044</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -577,106 +582,102 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>process profile</t>
+          <t>frequency</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>b is a process_profile =Def. there is some process c such that b process_profile_of c (axiom label in BFO2 Reference: [093-002])</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>A physical quality which inheres in a bearer by virtue of the number of the bearer's repetitive actions in a particular time.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BCIO:043000</t>
+          <t>BFO:0000031</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>generically dependent continuant</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>process attribute</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>A process profile that is an attribute of a process.</t>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>b is a generically dependent continuant = Def. b is a continuant that g-depends_on one or more other entities. (axiom label in BFO2 Reference: [074-001])</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BCIO:050315</t>
+          <t>IAO:0000030</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>information content entity</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>BCI attribute</t>
-        </is>
-      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>A process attribute whose bearer is a behaviour change intervention.</t>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>A generically dependent continuant that is about some thing.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BCIO:008580</t>
+          <t>IAO:0000027</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>data item</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>order of BCI temporal parts</t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>A &lt;BCI attribute&gt; that is the  temporal positioning of BCI temporal parts.</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>"After questionnaires were completed, feedback was selected
-out of a database with messages for each possible combination
-of answers."; "The PA advice started with a general introduction,
-followed by normative feedback, which related students’ PA
-levels to the PA guidelines."</t>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>An information content entity that is intended to be a truthful statement about something (modulo, e.g., measurement precision or other systematic errors) and is constructed/acquired by a method which reliably tends to produce (approximately) truthful statements.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BCIO:008500</t>
+          <t>BCIO:051005</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -684,30 +685,27 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>BCI schedule of delivery</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>number of intervention contact events</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>A &lt;BCI attribute&gt; that is its temporal organisation</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>A &lt;data item&gt; that is the number of contact events in an intervention temporal part.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Includes the start and end of a BCI, its parts, and their organisation around relevant timepoints.</t>
-        </is>
-      </c>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BCIO:008535</t>
+          <t>BCIO:008515</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -716,34 +714,35 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>regular intervention schedule</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>A &lt;BCI schedule of delivery&gt; in which the frequency and duration of Intervention temporal parts are uniform across the course of a BCI or BCI part.</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>number of BCI contact events</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>A &lt;number of intervention contact events&gt; that is the number of contact events in a BCI temporal part.</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>the length and regularity of sessions were consistent across the duration of the intervention, taking place for an hour each week</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>A type of schedule which plans that the duration and frequency of sessions or digital contacts remain constant across the course of an intervention</t>
+          <t>The planned total number of sessions or digital contacts in an intervention or part</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>one; 6; 12; twenty</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BCIO:008540</t>
+          <t>BCIO:051004</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -751,83 +750,100 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>intervention temporal part frequency</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>irregular intervention schedule</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>A &lt;BCI schedule of delivery&gt; in which the frequency and duration of contact events change over the course of a temporal part or BCI.</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>A &lt;data item&gt; that is how often intervention temporal parts occur within an intervention.</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>telephone feedback sessions were more frequent during the first 6 weeks; participants were free to access the app whenever they desired</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>A type of schedule which plans that the duration and frequency of sessions or digital contacts vary across the course of an intervention</t>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>This is useful when grouping contact events together to the schedule of an intervention. For example, authors may describe participants as taking part in 90 minutes of physical activity weekly. These 90 minutes could be split across several contact events, however together these contact events form an intervention part which occurs weekly.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OBI:0000011</t>
+          <t>BCIO:008710</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>planned process</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>BCI temporal part frequency</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>A process that realizes a plan which is the concretization of a plan specification.</t>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>An &lt;intervention temporal part frequency&gt; that is how often intervention temporal parts occur within a BCI.</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>How often intervention parts are planned to occur</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>This is useful when grouping contact events together to the schedule of an intervention. For example, authors may describe participants as taking part in 90 minutes of physical activity weekly. These 90 minutes could be split across several contact events, however together these contact events form an intervention part which occurs weekly.; Participants took part in 90 minutes of PA "weekly"</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BCIO:037000</t>
+          <t>BCIO:050504</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>intervention</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>total intervention contact event duration statistic</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>A planned process that has the aim of influencing an outcome.</t>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>A &lt;data item&gt; that is about a collection of total contact event durations.</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCIO:003000</t>
+          <t>BCIO:050495</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -835,62 +851,63 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>behaviour change intervention</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>mean total intervention contact event duration</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>An intervention that has the aim of influencing human behaviour.</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>A &lt;total intervention contact event duration statistic&gt; that is the average value calculated from a collection of total contact event durations.</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BCIO:008505</t>
+          <t>BCIO:050499</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>BCI temporal part</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>median total intervention contact event duration</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>A &lt;planned process&gt; that is a part of a BCI.</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>A &lt;total intervention contact event duration statistic&gt; that is the central value of a collection of total contact event durations when they are arranged in ascending order.</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Temporal parts are defined by the authors of reports. They usually group contact events with similar delivery (e.g. face-to-face), content (e.g. CBT), or contextual features (e.g. school lessons), in order to describe their schedule.; counselling sessions; the first 6 weeks of the intervention; group discussion; a presentation; the last 4 weeks of the intervention</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>A planned part of an intervention</t>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BCIO:008510</t>
+          <t>BCIO:050503</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -898,435 +915,479 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>BCI contact event</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>minimum total intervention contact event duration</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>A &lt;BCI temporal part&gt; that is an occasion in which a member of a BCI population comes into contact with a BCI.</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>A &lt;total intervention contact event duration statistic&gt; that is the lowest value from a collection of total contact event durations.</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>All contact events are temporal parts, but not all temporal parts are contact events. Whilst contact events are single continuous events, temporal parts of an intervention can  group together multiple different contact events which might have similar features. For example, a set of 10 counselling sessions might be a temporal part within an intervention. The same intervention can have a set of 5 exercise sessions. These 5 sessions together make up another temporal part. Each single session within these parts  is a contact event.; A counselling session; An online chat session; An advertisement display.</t>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BFO:0000008</t>
+          <t>BCIO:050910</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>temporal region</t>
-        </is>
-      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>maximum total intervention contact event duration</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>A &lt;total intervention contact event duration statistic&gt; that is the highest value from a collection of total contact event durations.</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BFO:0000038</t>
+          <t>BCIO:050905</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>one-dimensional temporal region</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>intervention duration statistic</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>A one-dimensional temporal region is a temporal region that is extended.</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>A &lt;data item&gt; that is about a collection of intervention durations.</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BCIO:008575</t>
+          <t>BCIO:050909</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>interval between BCI temporal parts</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>mean intervention duration</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>A &lt;temporal interval&gt; between the end of one BCI temporal part and the beginning of a subsequent BCI temporal part.</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>An &lt;intervention duration statistic&gt; that is the average value calculated from a collection of intervention durations.</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>"2 weeks"; "1 day"</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>The planned duration of a break between two parts of an intervention</t>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BCIO:008525</t>
+          <t>BCIO:050908</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>BCI contact event duration</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>maximum intervention duration</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>A &lt;temporal interval&gt; between the start and end of a BCI contact event.</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>An &lt;intervention duration statistic&gt; that is the highest value from a collection of intervention durations.</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>1 hour; 30 minutes; 2 minutes</t>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BCIO:008545</t>
+          <t>BCIO:050501</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>total BCI contact event duration</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>minimum intervention duration</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>A &lt;temporal interval&gt; that is the total of intervention temporal parts within a behaviour change intervention.</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>An &lt;intervention duration statistic&gt; that is the lowest value from a collection of intervention durations.</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>150 minutes; 12 hours</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>The planned total duration of all sessions or digital contacts in an intervention or part</t>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BCIO:008560</t>
+          <t>BCIO:050498</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>BCI duration</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>median intervention duration</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>A &lt;temporal interval&gt; between the start and end of a BCI.</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>An &lt;intervention duration statistic&gt; that is the central value of a collection of intervention durations when they are arranged in ascending order.</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>6 weeks; 2 months; 1 year</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>The planned duration of an intervention</t>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BCIO:008565</t>
+          <t>BCIO:050516</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>BCI temporal part duration</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>intervention temporal part frequency statistic</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>A &lt;temporal interval&gt; between the start and end of an intervention temporal part.</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>A &lt;data item&gt; that is about a collection of intervention temporal part frequencies.</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>6 weeks; 2 weeks</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>The planned duration of a part of an intervention</t>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BCIO:008530</t>
+          <t>BCIO:050520</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>temporal reference associated with the intervention</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>minimum intervention temporal part frequency statistic</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>A &lt;temporal region&gt; against which a BCI  temporal part is referenced.</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>An &lt;intervention temporal part frequency statistic&gt; that is the lowest value from a collection of intervention temporal part frequencies.</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Temporal references are used by authors when there is a behaviourally relevant event which structures the schedule of a BCI. This can include things like quit dates, childbirth, medical operations etc.
-We often refer to timepoints when we mean a specific time or some extended period (e.g., Monday). This class allows for the natural usage of a term while maintaining ontological coherence.; A feedback call was scheduled to be delivered around 6 months after the birth of the baby; The smoking intervention started 2 weeks after participants were enrolled into an inpatient setting</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>A statement which describes how the delivery of intervention parts is scheduled relative to associated external events.</t>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BFO:0000002</t>
+          <t>BCIO:050517</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>continuant</t>
-        </is>
-      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>maximum intervention temporal part frequency statistic</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>An entity that exists in full at any time in which it exists at all, persists through time while maintaining its identity and has no temporal parts.</t>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>An &lt;intervention temporal part frequency statistic&gt; that is the highest value from a collection of intervention temporal part frequencies.</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BFO:0000020</t>
+          <t>BCIO:050519</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>characteristic</t>
-        </is>
-      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>median intervention temporal part frequency statistic</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>b is a specifically dependent continuant = Def. b is a continuant &amp; there is some independent continuant c which is not a spatial region and which is such that b s-depends_on c at every time t during the course of b’s existence. (axiom label in BFO2 Reference: [050-003])</t>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>An &lt;intervention temporal part frequency statistic&gt; that is the central value of a collection of intervention temporal part frequencies when they are arranged in ascending order.</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PATO:0000044</t>
+          <t>BCIO:050518</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>frequency</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>mean intervention temporal part frequency statistic</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>A physical quality which inheres in a bearer by virtue of the number of the bearer's repetitive actions in a particular time.</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>An &lt;intervention temporal part frequency statistic&gt; that is the average value calculated from a collection of intervention temporal part frequencies.</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BFO:0000031</t>
+          <t>BCIO:050505</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>generically dependent continuant</t>
-        </is>
-      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>intervention contact event duration statistic</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>b is a generically dependent continuant = Def. b is a continuant that g-depends_on one or more other entities. (axiom label in BFO2 Reference: [074-001])</t>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>A &lt;data item&gt; that is about a collection of intervention contact event durations.</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IAO:0000030</t>
+          <t>BCIO:050511</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>information content entity</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>median intervention contact event duration</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>A generically dependent continuant that is about some thing.</t>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>An &lt;intervention contact event duration statistic&gt; that is the central value of a collection of intervention contact event durations when they are arranged in ascending order.</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IAO:0000027</t>
+          <t>BCIO:050513</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>data item</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>minimum intervention contact event duration</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>An information content entity that is intended to be a truthful statement about something (modulo, e.g., measurement precision or other systematic errors) and is constructed/acquired by a method which reliably tends to produce (approximately) truthful statements.</t>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>An &lt;intervention contact event duration statistic&gt; that is the lowest value from a collection of intervention contact event durations.</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BCIO:050504</t>
+          <t>BCIO:050507</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1334,26 +1395,31 @@
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>total BCI contact event duration statistic</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>maximum intervention contact event duration</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>A &lt;data item&gt; that is about a collection of total contact event durations.</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>An &lt;intervention contact event duration statistic&gt; that is the highest value from a collection of intervention contact event durations.</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BCIO:050910</t>
+          <t>BCIO:050509</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1364,23 +1430,28 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>maximum total BCI contact event duration</t>
+          <t>mean intervention contact event duration</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>A &lt;total contact event duration statistic&gt; that is the highest value from a collection of total contact event durations.</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>An &lt;intervention contact event duration statistic&gt; that is the average value calculated from a collection of intervention contact event durations.</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BCIO:050503</t>
+          <t>BCIO:051001</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1388,26 +1459,27 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>minimum total BCI contact event duration</t>
-        </is>
-      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>intervention contact event frequency</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>A &lt;total contact event duration statistic&gt; that is the lowest value from a collection of total contact event durations.</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>A &lt;data item&gt; about the number times an intervention contact event occurs per unit of time.</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BCIO:050495</t>
+          <t>BCIO:008700</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1418,23 +1490,33 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>mean total BCI contact event duration</t>
+          <t>BCI contact event frequency</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>A &lt;total contact event duration statistic&gt; that is the average value calculated from a collection of total contact event durations.</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>An &lt;intervention contact event frequency&gt; about the number times a BCI contact event occurs per unit of time.</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>How often intervention sessions or digital contacts are planned to occur</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>twice a week; daily; one a week</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BCIO:050499</t>
+          <t>BCIO:050903</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1442,26 +1524,31 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>median total BCI contact event duration</t>
-        </is>
-      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>intervention contact event frequency statistic</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>A &lt;total contact event duration statistic&gt; that is the central value of a collection of total contact event durations when they are arranged in ascending order.</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>A &lt;data item&gt; that is about a collection of intervention contact event frequencies.</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BCIO:008700</t>
+          <t>BCIO:050906</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1469,35 +1556,31 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>BCI contact event frequency</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>maximum intervention contact event frequency</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>A &lt;data item&gt; about the number times a contact event occurs per unit of time.</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>An &lt;intervention contact event frequency statistic&gt; that is the highest value from a collection of intervention contact event frequencies.</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>twice a week; daily; one a week</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>How often intervention sessions or digital contacts are planned to occur</t>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BCIO:050516</t>
+          <t>BCIO:050911</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1505,26 +1588,31 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>BCI temporal part frequency statistic</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>mean intervention contact event frequency</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>A &lt;data item&gt; that is about a collection of BCI temporal part frequencies.</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>An &lt;intervention contact event frequency statistic&gt; that is the average value calculated from a collection of intervention contact event frequencies.</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BCIO:050517</t>
+          <t>BCIO:050500</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1535,23 +1623,28 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>maximum BCI temporal part frequency statistic</t>
+          <t>minimum intervention contact event frequency</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>A &lt;BCI temporal part frequency statistic&gt; that is the highest value from a collection of BCI temporal part frequencies.</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>An &lt;intervention contact event frequency statistic&gt; that is the lowest value from a collection of intervention contact event frequencies.</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BCIO:050520</t>
+          <t>BCIO:050496</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1562,23 +1655,28 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>minimum BCI temporal part frequency statistic</t>
+          <t>median intervention contact event frequency</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>A &lt;BCI temporal part frequency statistic&gt; that is the lowest value from a collection of BCI temporal part frequencies.</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>An &lt;intervention contact event frequency statistic&gt; that is the central value of a collection of  intervention contact event frequencies when they are arranged in ascending order.</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BCIO:050518</t>
+          <t>BCIO:050506</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1586,26 +1684,31 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>mean BCI temporal part frequency statistic</t>
-        </is>
-      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>intervention temporal part duration statistic</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>A &lt;BCI temporal part frequency statistic&gt; that is the average value calculated from a collection of BCI temporal part frequencies.</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>A &lt;data item&gt; that is about a collection of intervention temporal part durations.</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BCIO:050519</t>
+          <t>BCIO:050508</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1616,23 +1719,28 @@
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>median BCI temporal part frequency statistic</t>
+          <t>maximum intervention temporal part duration</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>A &lt;BCI temporal part frequency statistic&gt; that is the central value of a collection of BCI temporal part frequencies when they are arranged in ascending order.</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>An &lt;intervention temporal part duration statistic&gt; that denotes the highest value from a collection of intervention temporal part durations.</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BCIO:050505</t>
+          <t>BCIO:050510</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1640,26 +1748,31 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>BCI contact event duration statistic</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>mean intervention temporal part duration</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>A &lt;data item&gt; that is about a collection of BCI contact event durations.</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>An &lt;intervention temporal part duration statistic&gt; that is the average value calculated from a collection of intervention temporal part durations.</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BCIO:050513</t>
+          <t>BCIO:050512</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1670,23 +1783,28 @@
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>minimum BCI contact event duration</t>
+          <t>median intervention temporal part duration</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>A &lt;BCI contact event duration statistic&gt; that is the lowest value from a collection of BCI contact event durations.</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>An &lt;intervention temporal part duration statistic&gt; that is the central value of a collection of intervention temporal part durations when they are arranged in ascending order.</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BCIO:050509</t>
+          <t>BCIO:050514</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1697,23 +1815,28 @@
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>mean BCI contact event duration</t>
+          <t>minimum intervention temporal part duration</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>A &lt;BCI contact event duration statistic&gt; that is the average value calculated from a collection of BCI contact event durations.</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>An &lt;intervention temporal part duration statistic&gt; that denotes the lowest value from a collection of intervention temporal part durations.</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BCIO:050511</t>
+          <t>BCIO:050904</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -1721,26 +1844,31 @@
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>median BCI contact event duration</t>
-        </is>
-      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>intervention contact event number statistic</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>A &lt;BCI contact event duration statistic&gt; that is the central value of a collection of BCI contact event durations when they are arranged in ascending order.</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>A &lt;data item&gt; that is about a collection of intervention contact event numbers.</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BCIO:050507</t>
+          <t>BCIO:050912</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -1751,23 +1879,28 @@
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>maximum BCI contact event duration</t>
+          <t>mean intervention contact event number</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>A &lt;BCI contact event duration statistic&gt; that is the highest value from a collection of BCI contact event durations.</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>An &lt;intervention contact event number statistic&gt; that is the average value calculated from a collection of intervention contact event numbers.</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BCIO:050506</t>
+          <t>BCIO:050497</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -1775,26 +1908,31 @@
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>BCI temporal part duration statistic</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>median intervention contact event number</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>A &lt;data item&gt; that is about a collection of intervention temporal part durations.</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>An &lt;intervention contact event number statistic&gt; that is the central value of a collection of  intervention contact event numbers when they are arranged in ascending order.</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BCIO:050514</t>
+          <t>BCIO:050502</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -1805,23 +1943,28 @@
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>minimum BCI temporal part duration</t>
+          <t>minimum intervention contact event number</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>A &lt;BCI temporal part duration statistic&gt; that denotes the lowest value from a collection of BCI temporal part durations.</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>An &lt;intervention contact event number statistic&gt; that is the lowest value from a collection of intervention contact event numbers.</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BCIO:050508</t>
+          <t>BCIO:050907</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -1832,131 +1975,129 @@
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>maximum BCI temporal part duration</t>
+          <t>maximum intervention contact event number</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>A &lt;BCI temporal part duration statistic&gt; that denotes the highest value from a collection of BCI temporal part durations.</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>An &lt;intervention contact event number statistic&gt; that is the highest value from a collection of intervention contact event numbers.</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BCIO:050510</t>
+          <t>BFO:0000003</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>occurrent</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>mean BCI temporal part duration</t>
-        </is>
-      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>A &lt;BCI temporal part duration statistic&gt; that is the average value calculated from a collection of BCI temporal part durations.</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>An entity that has temporal parts and that happens, unfolds or develops through time.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BCIO:050512</t>
+          <t>BFO:0000008</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>temporal region</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>median BCI temporal part duration</t>
-        </is>
-      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>A &lt;BCI temporal part duration statistic&gt; that is the central value of a collection of BCI temporal part durations when they are arranged in ascending order.</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BCIO:050903</t>
+          <t>BFO:0000038</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>temporal interval</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>BCI contact event frequency statistic</t>
-        </is>
-      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>A &lt;data item&gt; that is about a collection of BCI contact event frequencies.</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region is a temporal region that is extended.</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BCIO:050911</t>
+          <t>BCIO:051018</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>intervention contact event duration</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>mean BCI contact event frequency</t>
-        </is>
-      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>A &lt;BCI contact event frequency statistic&gt; that is the average value calculated from a collection of BCI contact event frequencies.</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>A &lt;temporal interval&gt; between the start and end of an intervention contact event.</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BCIO:050496</t>
+          <t>BCIO:008525</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -1964,53 +2105,59 @@
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>median BCI contact event frequency</t>
-        </is>
-      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>BCI contact event duration</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>A &lt;BCI contact event frequency statistic&gt; that is the central value of a collection of  BCI contact event frequencies when they are arranged in ascending order.</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>An &lt;intervention contact event duration&gt; between the start and end of a BCI contact event.</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>1 hour; 30 minutes; 2 minutes</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BCIO:050500</t>
+          <t>BCIO:051002</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>intervention duration</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>minimum BCI contact event frequency</t>
-        </is>
-      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>A &lt;BCI contact event frequency statistic&gt; that is the lowest value from a collection of BCI contact event frequencies.</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>A &lt;temporal interval&gt; between the start and end of an intervention.</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BCIO:050906</t>
+          <t>BCIO:008560</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2018,53 +2165,64 @@
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>maximum BCI contact event frequency</t>
-        </is>
-      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>BCI duration</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>A &lt;BCI contact event frequency statistic&gt; that is the highest value from a collection of BCI contact event frequencies.</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>An &lt;intervention duration&gt; between the start and end of a BCI.</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>The planned duration of an intervention</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>6 weeks; 2 months; 1 year</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BCIO:050904</t>
+          <t>BCIO:051017</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>BCI contact event number statistic</t>
-        </is>
-      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>interval between intervention temporal parts</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>A &lt;data item&gt; that is about a collection of BCI contact event numbers.</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>A &lt;temporal interval&gt; between the end of one intervention temporal part and the beginning of a subsequent intervention temporal part.</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BCIO:050907</t>
+          <t>BCIO:008575</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2072,53 +2230,64 @@
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>maximum BCI contact event number</t>
-        </is>
-      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>interval between BCI temporal parts</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>A &lt;BCI contact event number statistic&gt; that is the highest value from a collection of BCI contact event numbers.</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>An &lt;interval between intervention temporal parts&gt; between the end of one BCI temporal part and the beginning of a subsequent BCI temporal part.</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>The planned duration of a break between two parts of an intervention</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>"2 weeks"; "1 day"</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BCIO:050912</t>
+          <t>BCIO:051003</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>intervention temporal part duration</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>mean BCI contact event number</t>
-        </is>
-      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>A &lt;BCI contact event number statistic&gt; that is the average value calculated from a collection of BCI contact event numbers.</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>A &lt;temporal interval&gt; between the start and end of an intervention temporal part.</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BCIO:050502</t>
+          <t>BCIO:008565</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2126,53 +2295,64 @@
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>minimum BCI contact event number</t>
-        </is>
-      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>BCI temporal part duration</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>A &lt;BCI contact event number statistic&gt; that is the lowest value from a collection of BCI contact event numbers.</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>An &lt;intervention temporal part duration&gt; between the start and end of a behaviour change intervention temporal part.</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>The planned duration of a part of an intervention</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>6 weeks; 2 weeks</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BCIO:050497</t>
+          <t>BCIO:051006</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>total intervention contact event duration</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>median BCI contact event number</t>
-        </is>
-      </c>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>A &lt;BCI contact event number statistic&gt; that is the central value of a collection of  BCI contact event numbers when they are arranged in ascending order.</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>A &lt;temporal interval&gt; that is the total of intervention temporal parts within an intervention.</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BCIO:008515</t>
+          <t>BCIO:008545</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2182,177 +2362,185 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>number of BCI contact events</t>
+          <t>total BCI contact event duration</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>A &lt;data item&gt; that is the number of contact events in a BCI temporal part.</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>A &lt;total intervention contact event duration&gt; that is the total of intervention temporal parts within a behaviour change intervention.</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>one; 6; 12; twenty</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>The planned total number of sessions or digital contacts in an intervention or part</t>
+          <t>The planned total duration of all sessions or digital contacts in an intervention or part</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>150 minutes; 12 hours</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BCIO:008710</t>
+          <t>BCIO:051015</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>temporal reference associated with the intervention</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>BCI temporal part frequency</t>
-        </is>
-      </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>A &lt;data item&gt; that is how often intervention temporal parts occur within a BCI.</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>A &lt;temporal region&gt; against which an intervention  temporal part is referenced.</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>This is useful when grouping contact events together to the schedule of an intervention. For example, authors may describe participants as taking part in 90 minutes of physical activity weekly. These 90 minutes could be split across several contact events, however together these contact events form an intervention part which occurs weekly.; Participants took part in 90 minutes of PA "weekly"</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>How often intervention parts are planned to occur</t>
+          <t>A statement which describes how the delivery of intervention parts is scheduled relative to associated external events.</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Temporal references are used by authors when there is a behaviourally relevant event which structures the schedule of a BCI. This can include things like quit dates, childbirth, medical operations etc.
+We often refer to timepoints when we mean a specific time or some extended period (e.g., Monday). This class allows for the natural usage of a term while maintaining ontological coherence.; A feedback call was scheduled to be delivered around 6 months after the birth of the baby; The smoking intervention started 2 weeks after participants were enrolled into an inpatient setting</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BCIO:050905</t>
+          <t>BCIO:008530</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>BCI duration statistic</t>
-        </is>
-      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>temporal reference associated with the BCI</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>A &lt;data item&gt; that is about a collection of BCI durations.</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>A &lt;temporal reference associated with the intervention&gt; against which a BCI  temporal part is referenced.</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>A statement which describes how the delivery of intervention parts is scheduled relative to associated external events.</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Temporal references are used by authors when there is a behaviourally relevant event which structures the schedule of a BCI. This can include things like quit dates, childbirth, medical operations etc.
+We often refer to timepoints when we mean a specific time or some extended period (e.g., Monday). This class allows for the natural usage of a term while maintaining ontological coherence.; A feedback call was scheduled to be delivered around 6 months after the birth of the baby; The smoking intervention started 2 weeks after participants were enrolled into an inpatient setting</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BCIO:050501</t>
+          <t>BFO:0000015</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>minimum BCI duration</t>
-        </is>
-      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>A &lt;BCI duration statistic&gt; that is the lowest value from a collection of BCI durations.</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>An occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BCIO:050908</t>
+          <t>BFO:0000144</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>process profile</t>
+        </is>
+      </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>maximum BCI duration</t>
-        </is>
-      </c>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>A &lt;BCI duration statistic&gt; that is the highest value from a collection of BCI durations.</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>b is a process_profile =Def. there is some process c such that b process_profile_of c (axiom label in BFO2 Reference: [093-002])</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BCIO:050498</t>
+          <t>BCIO:043000</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>process attribute</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>median BCI duration</t>
-        </is>
-      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>A &lt;BCI duration statistic&gt; that is the central value of a collection of BCI durations when they are arranged in ascending order.</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>A process profile that is an attribute of a process.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BCIO:050909</t>
+          <t>BCIO:051010</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2360,21 +2548,522 @@
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>mean BCI duration</t>
-        </is>
-      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>intervention attribute</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>A &lt;BCI duration statistic&gt; that is the average value calculated from a collection of BCI durations.</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>A &lt;process attribute&gt; whose bearer is an intervention.</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>BCIO:051012</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>order of intervention temporal parts</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>An &lt;intervention attribute&gt; that is the  temporal positioning of intervention temporal parts.</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>BCIO:008580</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>order of BCI temporal parts</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>An &lt;order of intervention temporal parts&gt; that is the  temporal positioning of BCI temporal parts.</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>"After questionnaires were completed, feedback was selected
+out of a database with messages for each possible combination
+of answers."; "The PA advice started with a general introduction,
+followed by normative feedback, which related students’ PA
+levels to the PA guidelines."</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>BCIO:051011</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>intervention schedule of delivery</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>An &lt;intervention attribute&gt; that is its temporal organisation.</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>BCIO:051013</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>irregular intervention schedule</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>An &lt;intervention schedule of delivery&gt; in which the frequency and duration of contact events change over the course of a temporal part or intervention.</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>A type of schedule which plans that the duration and frequency of sessions or digital contacts vary across the course of an intervention</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>telephone feedback sessions were more frequent during the first 6 weeks; participants were free to access the app whenever they desired</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>BCIO:008540</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>irregular BCI schedule</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>An &lt;irregular intervention schedule&gt; in which the frequency and duration of contact events change over the course of a temporal part or intervention.</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>A type of schedule which plans that the duration and frequency of sessions or digital contacts vary across the course of an intervention</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>telephone feedback sessions were more frequent during the first 6 weeks; participants were free to access the app whenever they desired</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>BCIO:051014</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>regular intervention schedule</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>An &lt;intervention schedule of delivery&gt; in which the frequency and duration of intervention temporal parts are uniform across the course of an intervention or intervention part.</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>A type of schedule which plans that the duration and frequency of sessions or digital contacts remain constant across the course of an intervention</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>the length and regularity of sessions were consistent across the duration of the intervention, taking place for an hour each week</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>BCIO:008535</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>regular BCI schedule</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>A &lt;regular intervention schedule&gt; in which the frequency and duration of Intervention temporal parts are uniform across the course of an intervention or intervention part.</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>A type of schedule which plans that the duration and frequency of sessions or digital contacts remain constant across the course of an intervention</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>the length and regularity of sessions were consistent across the duration of the intervention, taking place for an hour each week</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>BCIO:050315</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>BCI attribute</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>A process attribute whose bearer is a behaviour change intervention.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>BCIO:008500</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>BCI schedule of delivery</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>A &lt;BCI attribute&gt; that is its temporal organisation</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Includes the start and end of a BCI, its parts, and their organisation around relevant timepoints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>OBI:0000011</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>planned process</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>A process that realizes a plan which is the concretization of a plan specification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>BCIO:051008</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>intervention temporal part</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>A &lt;planned process&gt; that is a part of an intervention.</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>BCIO:051009</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>intervention contact event</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>An &lt;intervention temporal part&gt; that is an occasion in which a member of an intervention population comes into contact with an intervention.</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>BCIO:008510</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>BCI contact event</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>An &lt;intervention contact event&gt; that is an occasion in which a member of a BCI population comes into contact with a BCI.</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>All contact events are temporal parts, but not all temporal parts are contact events. Whilst contact events are single continuous events, temporal parts of an intervention can  group together multiple different contact events which might have similar features. For example, a set of 10 counselling sessions might be a temporal part within an intervention. The same intervention can have a set of 5 exercise sessions. These 5 sessions together make up another temporal part. Each single session within these parts  is a contact event.; A counselling session; An online chat session; An advertisement display.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>BCIO:037000</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>intervention</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>A planned process that has the aim of influencing an outcome.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>BCIO:003000</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>behaviour change intervention</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>An intervention that has the aim of influencing human behaviour.</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>BCIO:008505</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>BCI temporal part</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>A &lt;planned process&gt; that is a part of a BCI.</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>A planned part of an intervention</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Temporal parts are defined by the authors of reports. They usually group contact events with similar delivery (e.g. face-to-face), content (e.g. CBT), or contextual features (e.g. school lessons), in order to describe their schedule.; counselling sessions; the first 6 weeks of the intervention; group discussion; a presentation; the last 4 weeks of the intervention</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Schedule/BCIO-schedule-hierarchy.xlsx
+++ b/Schedule/BCIO-schedule-hierarchy.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q85"/>
+  <dimension ref="A1:P68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,10 +434,14 @@
       <c r="G1" t="inlineStr"/>
       <c r="H1" t="inlineStr"/>
       <c r="I1" t="inlineStr"/>
-      <c r="J1" t="inlineStr"/>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
@@ -447,27 +451,22 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>examples</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>informaldefinition</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>subontology</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>synonyms</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>informaldefinition</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>subontology</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>examples</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>comment</t>
         </is>
       </c>
     </row>
@@ -489,8 +488,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>An entity is anything that exists or has existed or will exist.</t>
         </is>
@@ -514,8 +512,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>An entity is anything that exists or has existed or will exist.</t>
         </is>
@@ -539,8 +536,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>An entity that exists in full at any time in which it exists at all, persists through time while maintaining its identity and has no temporal parts.</t>
         </is>
@@ -564,10 +560,9 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>A continuant that inheres in or is borne by other entities. Every instance of A requires some specific instance of B which must always be the same.</t>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>b is a specifically dependent continuant = Def. b is a continuant and there is some independent continuant c which is not a spatial region and which is such that b s-depends_on c at every time t during the course of b’s existence. (axiom label in BFO2 Reference: [050-003])</t>
         </is>
       </c>
     </row>
@@ -589,8 +584,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>A physical quality which inheres in a bearer by virtue of the number of the bearer's repetitive actions in a particular time.</t>
         </is>
@@ -617,8 +611,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>b is a generically dependent continuant = Def. b is a continuant that g-depends_on one or more other entities. (axiom label in BFO2 Reference: [074-001])</t>
         </is>
@@ -642,8 +635,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>A generically dependent continuant that is about some thing.</t>
         </is>
@@ -667,8 +659,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>An information content entity that is intended to be a truthful statement about something (modulo, e.g., measurement precision or other systematic errors) and is constructed/acquired by a method which reliably tends to produce (approximately) truthful statements.</t>
         </is>
@@ -677,7 +668,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BCIO:051005</t>
+          <t>BCIO:050505</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -687,25 +678,28 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>number of intervention contact events</t>
+          <t>intervention contact event duration statistic</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>A &lt;data item&gt; that is the number of contact events in an intervention temporal part.</t>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>A &lt;data item&gt; that is about a collection of intervention contact event durations.</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BCIO:008515</t>
+          <t>BCIO:050513</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -716,33 +710,27 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>number of BCI contact events</t>
+          <t>minimum intervention contact event duration</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>A &lt;number of intervention contact events&gt; that is the number of contact events in a BCI temporal part.</t>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>An &lt;intervention contact event duration statistic&gt; that is the lowest value from a collection of intervention contact event durations.</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>The planned total number of sessions or digital contacts in an intervention or part</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>one; 6; 12; twenty</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BCIO:051004</t>
+          <t>BCIO:050507</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -750,31 +738,30 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>intervention temporal part frequency</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>maximum intervention contact event duration</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>A &lt;data item&gt; that is how often intervention temporal parts occur within an intervention.</t>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>An &lt;intervention contact event duration statistic&gt; that is the highest value from a collection of intervention contact event durations.</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>This is useful when grouping contact events together to the schedule of an intervention. For example, authors may describe participants as taking part in 90 minutes of physical activity weekly. These 90 minutes could be split across several contact events, however together these contact events form an intervention part which occurs weekly.</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BCIO:008710</t>
+          <t>BCIO:050511</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -785,33 +772,27 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>BCI temporal part frequency</t>
+          <t>median intervention contact event duration</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>An &lt;intervention temporal part frequency&gt; that is how often intervention temporal parts occur within a BCI.</t>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>An &lt;intervention contact event duration statistic&gt; that is the central value of a collection of intervention contact event durations when they are arranged in ascending order.</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>How often intervention parts are planned to occur</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>This is useful when grouping contact events together to the schedule of an intervention. For example, authors may describe participants as taking part in 90 minutes of physical activity weekly. These 90 minutes could be split across several contact events, however together these contact events form an intervention part which occurs weekly.; Participants took part in 90 minutes of PA "weekly"</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BCIO:050504</t>
+          <t>BCIO:050509</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -819,31 +800,30 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>total intervention contact event duration statistic</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>mean intervention contact event duration</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>A &lt;data item&gt; that is about a collection of total contact event durations.</t>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>An &lt;intervention contact event duration statistic&gt; that is the average value calculated from a collection of intervention contact event durations.</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCIO:050495</t>
+          <t>BCIO:050904</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -851,31 +831,30 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>mean total intervention contact event duration</t>
-        </is>
-      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>intervention contact event number statistic</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>A &lt;total intervention contact event duration statistic&gt; that is the average value calculated from a collection of total contact event durations.</t>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>A &lt;data item&gt; that is about a collection of intervention contact event numbers.</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BCIO:050499</t>
+          <t>BCIO:050502</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -886,28 +865,27 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>median total intervention contact event duration</t>
+          <t>minimum intervention contact event number</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>A &lt;total intervention contact event duration statistic&gt; that is the central value of a collection of total contact event durations when they are arranged in ascending order.</t>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>An &lt;intervention contact event number statistic&gt; that is the lowest value from a collection of intervention contact event numbers.</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BCIO:050503</t>
+          <t>BCIO:050497</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -918,28 +896,27 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>minimum total intervention contact event duration</t>
+          <t>median intervention contact event number</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>A &lt;total intervention contact event duration statistic&gt; that is the lowest value from a collection of total contact event durations.</t>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>An &lt;intervention contact event number statistic&gt; that is the central value of a collection of  intervention contact event numbers when they are arranged in ascending order.</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BCIO:050910</t>
+          <t>BCIO:050907</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -950,28 +927,27 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>maximum total intervention contact event duration</t>
+          <t>maximum intervention contact event number</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>A &lt;total intervention contact event duration statistic&gt; that is the highest value from a collection of total contact event durations.</t>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>An &lt;intervention contact event number statistic&gt; that is the highest value from a collection of intervention contact event numbers.</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BCIO:050905</t>
+          <t>BCIO:050912</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -979,31 +955,30 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>intervention duration statistic</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>mean intervention contact event number</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>A &lt;data item&gt; that is about a collection of intervention durations.</t>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>An &lt;intervention contact event number statistic&gt; that is the average value calculated from a collection of intervention contact event numbers.</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BCIO:050909</t>
+          <t>BCIO:050516</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1011,31 +986,30 @@
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>mean intervention duration</t>
-        </is>
-      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>intervention temporal part frequency statistic</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>An &lt;intervention duration statistic&gt; that is the average value calculated from a collection of intervention durations.</t>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>A &lt;data item&gt; that is about a collection of intervention temporal part frequencies.</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BCIO:050908</t>
+          <t>BCIO:050518</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1046,28 +1020,27 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>maximum intervention duration</t>
+          <t>mean intervention temporal part frequency statistic</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>An &lt;intervention duration statistic&gt; that is the highest value from a collection of intervention durations.</t>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>An &lt;intervention temporal part frequency statistic&gt; that is the average value calculated from a collection of intervention temporal part frequencies.</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BCIO:050501</t>
+          <t>BCIO:050519</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1078,28 +1051,27 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>minimum intervention duration</t>
+          <t>median intervention temporal part frequency statistic</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>An &lt;intervention duration statistic&gt; that is the lowest value from a collection of intervention durations.</t>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>An &lt;intervention temporal part frequency statistic&gt; that is the central value of a collection of intervention temporal part frequencies when they are arranged in ascending order.</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BCIO:050498</t>
+          <t>BCIO:050517</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1110,28 +1082,27 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>median intervention duration</t>
+          <t>maximum intervention temporal part frequency statistic</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>An &lt;intervention duration statistic&gt; that is the central value of a collection of intervention durations when they are arranged in ascending order.</t>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>An &lt;intervention temporal part frequency statistic&gt; that is the highest value from a collection of intervention temporal part frequencies.</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BCIO:050516</t>
+          <t>BCIO:050520</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1139,31 +1110,30 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>intervention temporal part frequency statistic</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>minimum intervention temporal part frequency statistic</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>A &lt;data item&gt; that is about a collection of intervention temporal part frequencies.</t>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>An &lt;intervention temporal part frequency statistic&gt; that is the lowest value from a collection of intervention temporal part frequencies.</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BCIO:050520</t>
+          <t>BCIO:050504</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1171,31 +1141,30 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>minimum intervention temporal part frequency statistic</t>
-        </is>
-      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>total intervention contact event duration</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>An &lt;intervention temporal part frequency statistic&gt; that is the lowest value from a collection of intervention temporal part frequencies.</t>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>A &lt;data item&gt; that is about the amount of time that the participant is exposed to the intervention through its contact events.</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; 150 minutes; 12 hours</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BCIO:050517</t>
+          <t>BCIO:050495</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1206,28 +1175,27 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>maximum intervention temporal part frequency statistic</t>
+          <t>mean total intervention contact event duration</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>An &lt;intervention temporal part frequency statistic&gt; that is the highest value from a collection of intervention temporal part frequencies.</t>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>A &lt;total intervention contact event duration&gt; that is the average value calculated from a collection of total contact event durations.</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BCIO:050519</t>
+          <t>BCIO:050910</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1238,28 +1206,27 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>median intervention temporal part frequency statistic</t>
+          <t>maximum total intervention contact event duration</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>An &lt;intervention temporal part frequency statistic&gt; that is the central value of a collection of intervention temporal part frequencies when they are arranged in ascending order.</t>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>A &lt;total intervention contact event duration&gt; that is the highest value from a collection of total contact event durations.</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BCIO:050518</t>
+          <t>BCIO:050499</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1270,28 +1237,27 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>mean intervention temporal part frequency statistic</t>
+          <t>median total intervention contact event duration</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>An &lt;intervention temporal part frequency statistic&gt; that is the average value calculated from a collection of intervention temporal part frequencies.</t>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>A &lt;total intervention contact event duration&gt; that is the central value of a collection of total contact event durations when they are arranged in ascending order.</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BCIO:050505</t>
+          <t>BCIO:050503</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1299,31 +1265,30 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>intervention contact event duration statistic</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>minimum total intervention contact event duration</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>A &lt;data item&gt; that is about a collection of intervention contact event durations.</t>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>A &lt;total intervention contact event duration&gt; that is the lowest value from a collection of total contact event durations.</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BCIO:050511</t>
+          <t>BCIO:050905</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1331,31 +1296,30 @@
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>median intervention contact event duration</t>
-        </is>
-      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>intervention duration statistic</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>An &lt;intervention contact event duration statistic&gt; that is the central value of a collection of intervention contact event durations when they are arranged in ascending order.</t>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>A &lt;data item&gt; that is about a collection of intervention durations.</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BCIO:050513</t>
+          <t>BCIO:050501</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1366,28 +1330,27 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>minimum intervention contact event duration</t>
+          <t>minimum intervention duration</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>An &lt;intervention contact event duration statistic&gt; that is the lowest value from a collection of intervention contact event durations.</t>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>An &lt;intervention duration statistic&gt; that is the lowest value from a collection of intervention durations.</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BCIO:050507</t>
+          <t>BCIO:050909</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1398,28 +1361,27 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>maximum intervention contact event duration</t>
+          <t>mean intervention duration</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>An &lt;intervention contact event duration statistic&gt; that is the highest value from a collection of intervention contact event durations.</t>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>An &lt;intervention duration statistic&gt; that is the average value calculated from a collection of intervention durations.</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BCIO:050509</t>
+          <t>BCIO:050498</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1430,28 +1392,27 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>mean intervention contact event duration</t>
+          <t>median intervention duration</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>An &lt;intervention contact event duration statistic&gt; that is the average value calculated from a collection of intervention contact event durations.</t>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>An &lt;intervention duration statistic&gt; that is the central value of a collection of intervention durations when they are arranged in ascending order.</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BCIO:051001</t>
+          <t>BCIO:050908</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1459,27 +1420,30 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>intervention contact event frequency</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>maximum intervention duration</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>A &lt;data item&gt; about the number times an intervention contact event occurs per unit of time.</t>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>An &lt;intervention duration statistic&gt; that is the highest value from a collection of intervention durations.</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BCIO:008700</t>
+          <t>BCIO:050506</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1487,36 +1451,30 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>BCI contact event frequency</t>
-        </is>
-      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>intervention temporal part duration statistic</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>An &lt;intervention contact event frequency&gt; about the number times a BCI contact event occurs per unit of time.</t>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>A &lt;data item&gt; that is about a collection of intervention temporal part durations.</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>How often intervention sessions or digital contacts are planned to occur</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>twice a week; daily; one a week</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BCIO:050903</t>
+          <t>BCIO:050512</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1524,31 +1482,30 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>intervention contact event frequency statistic</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>median intervention temporal part duration</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>A &lt;data item&gt; that is about a collection of intervention contact event frequencies.</t>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>An &lt;intervention temporal part duration statistic&gt; that is the central value of a collection of intervention temporal part durations when they are arranged in ascending order.</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BCIO:050906</t>
+          <t>BCIO:050508</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1559,28 +1516,27 @@
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>maximum intervention contact event frequency</t>
+          <t>maximum intervention temporal part duration</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>An &lt;intervention contact event frequency statistic&gt; that is the highest value from a collection of intervention contact event frequencies.</t>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>An &lt;intervention temporal part duration statistic&gt; that denotes the highest value from a collection of intervention temporal part durations.</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BCIO:050911</t>
+          <t>BCIO:050510</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1591,28 +1547,27 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>mean intervention contact event frequency</t>
+          <t>mean intervention temporal part duration</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>An &lt;intervention contact event frequency statistic&gt; that is the average value calculated from a collection of intervention contact event frequencies.</t>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>An &lt;intervention temporal part duration statistic&gt; that is the average value calculated from a collection of intervention temporal part durations.</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BCIO:050500</t>
+          <t>BCIO:050514</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1623,28 +1578,27 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>minimum intervention contact event frequency</t>
+          <t>minimum intervention temporal part duration</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>An &lt;intervention contact event frequency statistic&gt; that is the lowest value from a collection of intervention contact event frequencies.</t>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>An &lt;intervention temporal part duration statistic&gt; that denotes the lowest value from a collection of intervention temporal part durations.</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BCIO:050496</t>
+          <t>BCIO:008700</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1652,31 +1606,35 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>median intervention contact event frequency</t>
-        </is>
-      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>intervention contact event frequency</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>An &lt;intervention contact event frequency statistic&gt; that is the central value of a collection of  intervention contact event frequencies when they are arranged in ascending order.</t>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>A &lt;data item&gt; about the number times an intervention contact event occurs per unit of time.</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; twice a week; daily; one a week</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>How often intervention sessions or digital contacts are planned to occur</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BCIO:050506</t>
+          <t>BCIO:008515</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1686,29 +1644,33 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>intervention temporal part duration statistic</t>
+          <t>number of intervention contact events</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>A &lt;data item&gt; that is about a collection of intervention temporal part durations.</t>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>A &lt;data item&gt; that is the number of contact events in an intervention temporal part.</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; one; 6; 12; twenty</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>The planned total number of sessions or digital contacts in an intervention or part</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BCIO:050508</t>
+          <t>BCIO:050903</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1716,31 +1678,30 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>maximum intervention temporal part duration</t>
-        </is>
-      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>intervention contact event frequency statistic</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>An &lt;intervention temporal part duration statistic&gt; that denotes the highest value from a collection of intervention temporal part durations.</t>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>A &lt;data item&gt; that is about a collection of intervention contact event frequencies.</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BCIO:050510</t>
+          <t>BCIO:050500</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1751,28 +1712,27 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>mean intervention temporal part duration</t>
+          <t>minimum intervention contact event frequency</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>An &lt;intervention temporal part duration statistic&gt; that is the average value calculated from a collection of intervention temporal part durations.</t>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>An &lt;intervention contact event frequency statistic&gt; that is the lowest value from a collection of intervention contact event frequencies.</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BCIO:050512</t>
+          <t>BCIO:050906</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1783,28 +1743,27 @@
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>median intervention temporal part duration</t>
+          <t>maximum intervention contact event frequency</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>An &lt;intervention temporal part duration statistic&gt; that is the central value of a collection of intervention temporal part durations when they are arranged in ascending order.</t>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>An &lt;intervention contact event frequency statistic&gt; that is the highest value from a collection of intervention contact event frequencies.</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BCIO:050514</t>
+          <t>BCIO:050496</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1815,28 +1774,27 @@
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>minimum intervention temporal part duration</t>
+          <t>median intervention contact event frequency</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>An &lt;intervention temporal part duration statistic&gt; that denotes the lowest value from a collection of intervention temporal part durations.</t>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>An &lt;intervention contact event frequency statistic&gt; that is the central value of a collection of  intervention contact event frequencies when they are arranged in ascending order.</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BCIO:050904</t>
+          <t>BCIO:050911</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -1844,31 +1802,30 @@
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>intervention contact event number statistic</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>mean intervention contact event frequency</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>A &lt;data item&gt; that is about a collection of intervention contact event numbers.</t>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>An &lt;intervention contact event frequency statistic&gt; that is the average value calculated from a collection of intervention contact event frequencies.</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BCIO:050912</t>
+          <t>BCIO:008710</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -1876,228 +1833,226 @@
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>mean intervention contact event number</t>
-        </is>
-      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>intervention temporal part frequency</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>An &lt;intervention contact event number statistic&gt; that is the average value calculated from a collection of intervention contact event numbers.</t>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>A &lt;data item&gt; that is how often intervention temporal parts occur within an intervention.</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>This is useful when grouping contact events together to the schedule of an intervention. For example, authors may describe participants as taking part in 90 minutes of physical activity weekly. These 90 minutes could be split across several contact events, however together these contact events form an intervention part which occurs weekly. 
+This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; Participants took part in 90 minutes of PA "weekly"</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>How often intervention parts are planned to occur</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BCIO:050497</t>
+          <t>BFO:0000003</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>occurrent</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>median intervention contact event number</t>
-        </is>
-      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>An &lt;intervention contact event number statistic&gt; that is the central value of a collection of  intervention contact event numbers when they are arranged in ascending order.</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>An entity that has temporal parts and that happens, unfolds or develops through time.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BCIO:050502</t>
+          <t>BFO:0000015</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>minimum intervention contact event number</t>
-        </is>
-      </c>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>An &lt;intervention contact event number statistic&gt; that is the lowest value from a collection of intervention contact event numbers.</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>p is a process = Def. p is an occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t. (axiom label in BFO2 Reference: [083-003])</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BCIO:050907</t>
+          <t>BFO:0000144</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>process profile</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>maximum intervention contact event number</t>
-        </is>
-      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>An &lt;intervention contact event number statistic&gt; that is the highest value from a collection of intervention contact event numbers.</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>b is a process_profile =Def. there is some process c such that b process_profile_of c (axiom label in BFO2 Reference: [093-002])</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BFO:0000003</t>
+          <t>BCIO:043000</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>occurrent</t>
-        </is>
-      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>process attribute</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>An entity that has temporal parts and that happens, unfolds or develops through time.</t>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>A process profile that is an attribute of a process.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BFO:0000008</t>
+          <t>BCIO:051010</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>temporal region</t>
-        </is>
-      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>intervention attribute</t>
+        </is>
+      </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>A &lt;process attribute&gt; whose bearer is an intervention.</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BFO:0000038</t>
+          <t>BCIO:009000</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>temporal interval</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>intervention schedule of delivery</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>A one-dimensional temporal region is a temporal region that is extended.</t>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>An intervention attribute that is its temporal organisation.</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; Includes the start and end of the BCI and its parts.</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BCIO:051018</t>
+          <t>BCIO:008540</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>intervention contact event duration</t>
-        </is>
-      </c>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>A &lt;temporal interval&gt; between the start and end of an intervention contact event.</t>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>irregular intervention schedule</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>An &lt;intervention schedule of delivery&gt; in which the frequency and duration of contact events change over the course of a temporal part or intervention.</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; telephone feedback sessions were more frequent during the first 6 weeks; participants were free to access the app whenever they desired</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>A type of schedule which plans that the duration and frequency of sessions or digital contacts vary across the course of an intervention</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BCIO:008525</t>
+          <t>BCIO:008535</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2105,96 +2060,94 @@
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>BCI contact event duration</t>
-        </is>
-      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>An &lt;intervention contact event duration&gt; between the start and end of a BCI contact event.</t>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>regular intervention schedule</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>An &lt;intervention schedule of delivery&gt; in which the frequency and duration of Intervention temporal parts are uniform across the course of an intervention or intervention part.</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>1 hour; 30 minutes; 2 minutes</t>
-        </is>
-      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; the length and regularity of sessions were consistent across the duration of the intervention, taking place for an hour each week</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>A type of schedule which plans that the duration and frequency of sessions or digital contacts remain constant across the course of an intervention</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BCIO:051002</t>
+          <t>BCIO:008580</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>intervention duration</t>
-        </is>
-      </c>
+      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>order of intervention temporal parts</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>A &lt;temporal interval&gt; between the start and end of an intervention.</t>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>An &lt;intervention attribute&gt; that is the  temporal positioning of intervention temporal parts.</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; "After questionnaires were completed, feedback was selected
+out of a database with messages for each possible combination
+of answers."; "The PA advice started with a general introduction,
+followed by normative feedback, which related students’ PA
+levels to the PA guidelines."</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BCIO:008560</t>
+          <t>OBI:0000011</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>planned process</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>BCI duration</t>
-        </is>
-      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>An &lt;intervention duration&gt; between the start and end of a BCI.</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>The planned duration of an intervention</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>6 weeks; 2 months; 1 year</t>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>A process that realizes a plan which is the concretization of a plan specification.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BCIO:051017</t>
+          <t>BCIO:008505</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2203,26 +2156,35 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>interval between intervention temporal parts</t>
+          <t>intervention temporal part</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>A &lt;temporal interval&gt; between the end of one intervention temporal part and the beginning of a subsequent intervention temporal part.</t>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>A &lt;planned process&gt; that is a part of an intervention.</t>
         </is>
       </c>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Temporal parts are defined by the authors of reports. They usually group contact events with similar delivery (e.g. face-to-face), content (e.g. CBT), or contextual features (e.g. school lessons), in order to describe their schedule. 
+This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; counselling sessions; the first 6 weeks of the intervention; group discussion; a presentation; the last 4 weeks of the intervention</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>A planned part of an intervention</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BCIO:008575</t>
+          <t>BCIO:008510</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2232,34 +2194,29 @@
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>interval between BCI temporal parts</t>
+          <t>intervention contact event</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>An &lt;interval between intervention temporal parts&gt; between the end of one BCI temporal part and the beginning of a subsequent BCI temporal part.</t>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>An &lt;intervention temporal part&gt; that is an occasion in which a member of an intervention population comes into contact with an intervention.</t>
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>The planned duration of a break between two parts of an intervention</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>"2 weeks"; "1 day"</t>
-        </is>
-      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>All contact events are temporal parts, but not all temporal parts are contact events. Whilst contact events are single continuous events, temporal parts of an intervention can  group together multiple different contact events which might have similar features. For example, a set of 10 counselling sessions might be a temporal part within an intervention. The same intervention can have a set of 5 exercise sessions. These 5 sessions together make up another temporal part. Each single session within these parts  is a contact event.
+This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; A counselling session; An online chat session; An advertisement display.</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BCIO:051003</t>
+          <t>BCIO:037000</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2268,26 +2225,22 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>intervention temporal part duration</t>
+          <t>intervention</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>A &lt;temporal interval&gt; between the start and end of an intervention temporal part.</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>A planned process that has the aim of influencing an outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BCIO:008565</t>
+          <t>BCIO:003000</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2297,99 +2250,81 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>BCI temporal part duration</t>
+          <t>behaviour change intervention</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>An &lt;intervention temporal part duration&gt; between the start and end of a behaviour change intervention temporal part.</t>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>An intervention that has the aim of influencing human behaviour.</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>The planned duration of a part of an intervention</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>6 weeks; 2 weeks</t>
-        </is>
-      </c>
+      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BCIO:051006</t>
+          <t>BFO:0000008</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>temporal region</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>total intervention contact event duration</t>
-        </is>
-      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>A &lt;temporal interval&gt; that is the total of intervention temporal parts within an intervention.</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BCIO:008545</t>
+          <t>BCIO:008530</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>temporal reference associated with the intervention</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>total BCI contact event duration</t>
-        </is>
-      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>A &lt;total intervention contact event duration&gt; that is the total of intervention temporal parts within a behaviour change intervention.</t>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>A &lt;temporal region&gt; against which an intervention temporal part is referenced.</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Temporal references are used by authors when there is a behaviourally relevant event which structures the schedule of a BCI. This can include things like quit dates, childbirth, medical operations etc.
+We often refer to timepoints when we mean a specific time or some extended period (e.g., Monday). This class allows for the natural usage of a term while maintaining ontological coherence.
+This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; A feedback call was scheduled to be delivered around 6 months after the birth of the baby; The smoking intervention started 2 weeks after participants were enrolled into an inpatient setting</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>The planned total duration of all sessions or digital contacts in an intervention or part</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>150 minutes; 12 hours</t>
-        </is>
-      </c>
+          <t>A statement which describes how the delivery of intervention parts is scheduled relative to associated external events.</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BCIO:051015</t>
+          <t>BFO:0000038</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -2397,37 +2332,26 @@
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>temporal reference associated with the intervention</t>
+          <t>one-dimensional temporal region</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>A &lt;temporal region&gt; against which an intervention  temporal part is referenced.</t>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region is a temporal region that is extended.</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>A statement which describes how the delivery of intervention parts is scheduled relative to associated external events.</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>Temporal references are used by authors when there is a behaviourally relevant event which structures the schedule of a BCI. This can include things like quit dates, childbirth, medical operations etc.
-We often refer to timepoints when we mean a specific time or some extended period (e.g., Monday). This class allows for the natural usage of a term while maintaining ontological coherence.; A feedback call was scheduled to be delivered around 6 months after the birth of the baby; The smoking intervention started 2 weeks after participants were enrolled into an inpatient setting</t>
-        </is>
-      </c>
+      <c r="P64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BCIO:008530</t>
+          <t>BCIO:008575</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -2436,86 +2360,106 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>temporal reference associated with the BCI</t>
+          <t>interval between intervention temporal parts</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>A &lt;temporal reference associated with the intervention&gt; against which a BCI  temporal part is referenced.</t>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>A &lt;temporal interval&gt; between the end of one intervention temporal part and the beginning of a subsequent intervention temporal part.</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; "2 weeks"; "1 day"</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>A statement which describes how the delivery of intervention parts is scheduled relative to associated external events.</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>Temporal references are used by authors when there is a behaviourally relevant event which structures the schedule of a BCI. This can include things like quit dates, childbirth, medical operations etc.
-We often refer to timepoints when we mean a specific time or some extended period (e.g., Monday). This class allows for the natural usage of a term while maintaining ontological coherence.; A feedback call was scheduled to be delivered around 6 months after the birth of the baby; The smoking intervention started 2 weeks after participants were enrolled into an inpatient setting</t>
-        </is>
-      </c>
+          <t>The planned duration of a break between two parts of an intervention</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BFO:0000015</t>
+          <t>BCIO:008565</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>process</t>
-        </is>
-      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>intervention temporal part duration</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>An occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t.</t>
-        </is>
-      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>A &lt;temporal interval&gt; between the start and end of an intervention temporal part.</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; 6 weeks; 2 weeks</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>The planned duration of a part of an intervention</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BFO:0000144</t>
+          <t>BCIO:008560</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>process profile</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>intervention duration</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>b is a process_profile =Def. there is some process c such that b process_profile_of c (axiom label in BFO2 Reference: [093-002])</t>
-        </is>
-      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>A &lt;temporal interval&gt; between the start and end of an intervention.</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; 6 weeks; 2 months; 1 year</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>The planned duration of an intervention</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BCIO:043000</t>
+          <t>BCIO:008525</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -2524,546 +2468,24 @@
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>process attribute</t>
+          <t>intervention contact event duration</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>A process profile that is an attribute of a process.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>BCIO:051010</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr"/>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>intervention attribute</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>A &lt;process attribute&gt; whose bearer is an intervention.</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>BCIO:051012</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr"/>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>order of intervention temporal parts</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>An &lt;intervention attribute&gt; that is the  temporal positioning of intervention temporal parts.</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>BCIO:008580</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>order of BCI temporal parts</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>An &lt;order of intervention temporal parts&gt; that is the  temporal positioning of BCI temporal parts.</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>"After questionnaires were completed, feedback was selected
-out of a database with messages for each possible combination
-of answers."; "The PA advice started with a general introduction,
-followed by normative feedback, which related students’ PA
-levels to the PA guidelines."</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>BCIO:051011</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr"/>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>intervention schedule of delivery</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>An &lt;intervention attribute&gt; that is its temporal organisation.</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>BCIO:051013</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr"/>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>irregular intervention schedule</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>An &lt;intervention schedule of delivery&gt; in which the frequency and duration of contact events change over the course of a temporal part or intervention.</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>A type of schedule which plans that the duration and frequency of sessions or digital contacts vary across the course of an intervention</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>telephone feedback sessions were more frequent during the first 6 weeks; participants were free to access the app whenever they desired</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>BCIO:008540</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr"/>
-      <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>irregular BCI schedule</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>An &lt;irregular intervention schedule&gt; in which the frequency and duration of contact events change over the course of a temporal part or intervention.</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>A type of schedule which plans that the duration and frequency of sessions or digital contacts vary across the course of an intervention</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>telephone feedback sessions were more frequent during the first 6 weeks; participants were free to access the app whenever they desired</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>BCIO:051014</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>regular intervention schedule</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>An &lt;intervention schedule of delivery&gt; in which the frequency and duration of intervention temporal parts are uniform across the course of an intervention or intervention part.</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>A type of schedule which plans that the duration and frequency of sessions or digital contacts remain constant across the course of an intervention</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>the length and regularity of sessions were consistent across the duration of the intervention, taking place for an hour each week</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>BCIO:008535</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr"/>
-      <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>regular BCI schedule</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>A &lt;regular intervention schedule&gt; in which the frequency and duration of Intervention temporal parts are uniform across the course of an intervention or intervention part.</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>A type of schedule which plans that the duration and frequency of sessions or digital contacts remain constant across the course of an intervention</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>the length and regularity of sessions were consistent across the duration of the intervention, taking place for an hour each week</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>BCIO:050315</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
-      <c r="C77" t="inlineStr"/>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>BCI attribute</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>A process attribute whose bearer is a behaviour change intervention.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>BCIO:008500</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr"/>
-      <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>BCI schedule of delivery</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>A &lt;BCI attribute&gt; that is its temporal organisation</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Includes the start and end of a BCI, its parts, and their organisation around relevant timepoints.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>OBI:0000011</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr"/>
-      <c r="C79" t="inlineStr"/>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>planned process</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>A process that realizes a plan which is the concretization of a plan specification.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>BCIO:051008</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr"/>
-      <c r="C80" t="inlineStr"/>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>intervention temporal part</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>A &lt;planned process&gt; that is a part of an intervention.</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>BCIO:051009</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>intervention contact event</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>An &lt;intervention temporal part&gt; that is an occasion in which a member of an intervention population comes into contact with an intervention.</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>BCIO:008510</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr"/>
-      <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>BCI contact event</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>An &lt;intervention contact event&gt; that is an occasion in which a member of a BCI population comes into contact with a BCI.</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>All contact events are temporal parts, but not all temporal parts are contact events. Whilst contact events are single continuous events, temporal parts of an intervention can  group together multiple different contact events which might have similar features. For example, a set of 10 counselling sessions might be a temporal part within an intervention. The same intervention can have a set of 5 exercise sessions. These 5 sessions together make up another temporal part. Each single session within these parts  is a contact event.; A counselling session; An online chat session; An advertisement display.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>BCIO:037000</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
-      <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>intervention</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>A planned process that has the aim of influencing an outcome.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>BCIO:003000</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr"/>
-      <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>behaviour change intervention</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>An intervention that has the aim of influencing human behaviour.</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>BCIO:008505</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr"/>
-      <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>BCI temporal part</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>A &lt;planned process&gt; that is a part of a BCI.</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>A planned part of an intervention</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>Temporal parts are defined by the authors of reports. They usually group contact events with similar delivery (e.g. face-to-face), content (e.g. CBT), or contextual features (e.g. school lessons), in order to describe their schedule.; counselling sessions; the first 6 weeks of the intervention; group discussion; a presentation; the last 4 weeks of the intervention</t>
-        </is>
-      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>An &lt;temporal interval&gt; between the start and end of an intervention contact event.</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; 1 hour; 30 minutes; 2 minutes</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Schedule/BCIO-schedule-hierarchy.xlsx
+++ b/Schedule/BCIO-schedule-hierarchy.xlsx
@@ -446,27 +446,27 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>informaldefinition</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>synonyms</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>subontology</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>crossreference</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>examples</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>informaldefinition</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>subontology</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>synonyms</t>
         </is>
       </c>
     </row>
@@ -545,14 +545,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BFO:0000020</t>
+          <t>BFO:0000031</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>specifically dependent continuant</t>
+          <t>generically dependent continuant</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -562,14 +562,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>b is a specifically dependent continuant = Def. b is a continuant and there is some independent continuant c which is not a spatial region and which is such that b s-depends_on c at every time t during the course of b’s existence. (axiom label in BFO2 Reference: [050-003])</t>
+          <t>b is a generically dependent continuant = Def. b is a continuant that g-depends_on one or more other entities. (axiom label in BFO2 Reference: [074-001])</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PATO:0000044</t>
+          <t>IAO:0000030</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -577,7 +577,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>frequency</t>
+          <t>information content entity</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -586,89 +586,105 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>A physical quality which inheres in a bearer by virtue of the number of the bearer's repetitive actions in a particular time.</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+          <t>A generically dependent continuant that is about some thing.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BFO:0000031</t>
+          <t>IAO:0000027</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>generically dependent continuant</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>data item</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>b is a generically dependent continuant = Def. b is a continuant that g-depends_on one or more other entities. (axiom label in BFO2 Reference: [074-001])</t>
+          <t>An information content entity that is intended to be a truthful statement about something (modulo, e.g., measurement precision or other systematic errors) and is constructed/acquired by a method which reliably tends to produce (approximately) truthful statements.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IAO:0000030</t>
+          <t>BCIO:008700</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>information content entity</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>intervention contact event frequency</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>A generically dependent continuant that is about some thing.</t>
+          <t>A &lt;data item&gt; about the number times an intervention contact event occurs per unit of time.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>How often intervention sessions or digital contacts are planned to occur</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; twice a week; daily; one a week</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IAO:0000027</t>
+          <t>BCIO:050904</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>data item</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>intervention contact event number statistic</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>An information content entity that is intended to be a truthful statement about something (modulo, e.g., measurement precision or other systematic errors) and is constructed/acquired by a method which reliably tends to produce (approximately) truthful statements.</t>
+          <t>A &lt;data item&gt; that is about a collection of intervention contact event numbers.</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BCIO:050505</t>
+          <t>BCIO:050912</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -676,30 +692,30 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>intervention contact event duration statistic</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>mean intervention contact event number</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>A &lt;data item&gt; that is about a collection of intervention contact event durations.</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr"/>
+          <t>An &lt;intervention contact event number statistic&gt; that is the average value calculated from a collection of intervention contact event numbers.</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BCIO:050513</t>
+          <t>BCIO:050497</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -710,27 +726,27 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>minimum intervention contact event duration</t>
+          <t>median intervention contact event number</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>An &lt;intervention contact event duration statistic&gt; that is the lowest value from a collection of intervention contact event durations.</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr"/>
+          <t>An &lt;intervention contact event number statistic&gt; that is the central value of a collection of  intervention contact event numbers when they are arranged in ascending order.</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BCIO:050507</t>
+          <t>BCIO:050907</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -741,27 +757,27 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>maximum intervention contact event duration</t>
+          <t>maximum intervention contact event number</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>An &lt;intervention contact event duration statistic&gt; that is the highest value from a collection of intervention contact event durations.</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr"/>
+          <t>An &lt;intervention contact event number statistic&gt; that is the highest value from a collection of intervention contact event numbers.</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BCIO:050511</t>
+          <t>BCIO:050502</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -772,27 +788,27 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>median intervention contact event duration</t>
+          <t>minimum intervention contact event number</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>An &lt;intervention contact event duration statistic&gt; that is the central value of a collection of intervention contact event durations when they are arranged in ascending order.</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr"/>
+          <t>An &lt;intervention contact event number statistic&gt; that is the lowest value from a collection of intervention contact event numbers.</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BCIO:050509</t>
+          <t>BCIO:050903</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -800,30 +816,30 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>mean intervention contact event duration</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>intervention contact event frequency statistic</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>An &lt;intervention contact event duration statistic&gt; that is the average value calculated from a collection of intervention contact event durations.</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr"/>
+          <t>A &lt;data item&gt; that is about a collection of intervention contact event frequencies.</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCIO:050904</t>
+          <t>BCIO:050500</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -831,30 +847,30 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>intervention contact event number statistic</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>minimum intervention contact event frequency</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>A &lt;data item&gt; that is about a collection of intervention contact event numbers.</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr"/>
+          <t>An &lt;intervention contact event frequency statistic&gt; that is the lowest value from a collection of intervention contact event frequencies.</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BCIO:050502</t>
+          <t>BCIO:050496</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -865,27 +881,27 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>minimum intervention contact event number</t>
+          <t>median intervention contact event frequency</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>An &lt;intervention contact event number statistic&gt; that is the lowest value from a collection of intervention contact event numbers.</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr"/>
+          <t>An &lt;intervention contact event frequency statistic&gt; that is the central value of a collection of  intervention contact event frequencies when they are arranged in ascending order.</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BCIO:050497</t>
+          <t>BCIO:050906</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -896,27 +912,27 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>median intervention contact event number</t>
+          <t>maximum intervention contact event frequency</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>An &lt;intervention contact event number statistic&gt; that is the central value of a collection of  intervention contact event numbers when they are arranged in ascending order.</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr"/>
+          <t>An &lt;intervention contact event frequency statistic&gt; that is the highest value from a collection of intervention contact event frequencies.</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BCIO:050907</t>
+          <t>BCIO:050911</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -927,27 +943,27 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>maximum intervention contact event number</t>
+          <t>mean intervention contact event frequency</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>An &lt;intervention contact event number statistic&gt; that is the highest value from a collection of intervention contact event numbers.</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr"/>
+          <t>An &lt;intervention contact event frequency statistic&gt; that is the average value calculated from a collection of intervention contact event frequencies.</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BCIO:050912</t>
+          <t>BCIO:008710</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -955,30 +971,36 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>mean intervention contact event number</t>
-        </is>
-      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>intervention temporal part frequency</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>An &lt;intervention contact event number statistic&gt; that is the average value calculated from a collection of intervention contact event numbers.</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr"/>
+          <t>A &lt;data item&gt; that is how often intervention temporal parts occur within an intervention.</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>How often intervention parts are planned to occur</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>This is useful when grouping contact events together to the schedule of an intervention. For example, authors may describe participants as taking part in 90 minutes of physical activity weekly. These 90 minutes could be split across several contact events, however together these contact events form an intervention part which occurs weekly. 
+This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; Participants took part in 90 minutes of PA "weekly"</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BCIO:050516</t>
+          <t>BCIO:008515</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -988,28 +1010,33 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>intervention temporal part frequency statistic</t>
+          <t>number of intervention contact events</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>A &lt;data item&gt; that is about a collection of intervention temporal part frequencies.</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr"/>
+          <t>A &lt;data item&gt; that is the number of contact events in an intervention temporal part.</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>The planned total number of sessions or digital contacts in an intervention or part</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; one; 6; 12; twenty</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BCIO:050518</t>
+          <t>BCIO:050516</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1017,30 +1044,30 @@
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>mean intervention temporal part frequency statistic</t>
-        </is>
-      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>intervention temporal part frequency statistic</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>An &lt;intervention temporal part frequency statistic&gt; that is the average value calculated from a collection of intervention temporal part frequencies.</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr"/>
+          <t>A &lt;data item&gt; that is about a collection of intervention temporal part frequencies.</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BCIO:050519</t>
+          <t>BCIO:050518</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1051,22 +1078,22 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>median intervention temporal part frequency statistic</t>
+          <t>mean intervention temporal part frequency statistic</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>An &lt;intervention temporal part frequency statistic&gt; that is the central value of a collection of intervention temporal part frequencies when they are arranged in ascending order.</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr"/>
+          <t>An &lt;intervention temporal part frequency statistic&gt; that is the average value calculated from a collection of intervention temporal part frequencies.</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1091,18 +1118,18 @@
           <t>An &lt;intervention temporal part frequency statistic&gt; that is the highest value from a collection of intervention temporal part frequencies.</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BCIO:050520</t>
+          <t>BCIO:050519</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1113,27 +1140,27 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>minimum intervention temporal part frequency statistic</t>
+          <t>median intervention temporal part frequency statistic</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>An &lt;intervention temporal part frequency statistic&gt; that is the lowest value from a collection of intervention temporal part frequencies.</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr"/>
+          <t>An &lt;intervention temporal part frequency statistic&gt; that is the central value of a collection of intervention temporal part frequencies when they are arranged in ascending order.</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BCIO:050504</t>
+          <t>BCIO:050520</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1141,30 +1168,30 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>total intervention contact event duration</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>minimum intervention temporal part frequency statistic</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>A &lt;data item&gt; that is about the amount of time that the participant is exposed to the intervention through its contact events.</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; 150 minutes; 12 hours</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr"/>
+          <t>An &lt;intervention temporal part frequency statistic&gt; that is the lowest value from a collection of intervention temporal part frequencies.</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BCIO:050495</t>
+          <t>BCIO:050506</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1172,30 +1199,30 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>mean total intervention contact event duration</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>intervention temporal part duration statistic</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>A &lt;total intervention contact event duration&gt; that is the average value calculated from a collection of total contact event durations.</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr"/>
+          <t>A &lt;data item&gt; that is about a collection of intervention temporal part durations.</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BCIO:050910</t>
+          <t>BCIO:050512</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1206,27 +1233,27 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>maximum total intervention contact event duration</t>
+          <t>median intervention temporal part duration</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>A &lt;total intervention contact event duration&gt; that is the highest value from a collection of total contact event durations.</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr"/>
+          <t>An &lt;intervention temporal part duration statistic&gt; that is the central value of a collection of intervention temporal part durations when they are arranged in ascending order.</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BCIO:050499</t>
+          <t>BCIO:050508</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1237,27 +1264,27 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>median total intervention contact event duration</t>
+          <t>maximum intervention temporal part duration</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>A &lt;total intervention contact event duration&gt; that is the central value of a collection of total contact event durations when they are arranged in ascending order.</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr"/>
+          <t>An &lt;intervention temporal part duration statistic&gt; that denotes the highest value from a collection of intervention temporal part durations.</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BCIO:050503</t>
+          <t>BCIO:050514</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1268,27 +1295,27 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>minimum total intervention contact event duration</t>
+          <t>minimum intervention temporal part duration</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>A &lt;total intervention contact event duration&gt; that is the lowest value from a collection of total contact event durations.</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr"/>
+          <t>An &lt;intervention temporal part duration statistic&gt; that denotes the lowest value from a collection of intervention temporal part durations.</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BCIO:050905</t>
+          <t>BCIO:050510</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1296,30 +1323,30 @@
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>intervention duration statistic</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>mean intervention temporal part duration</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>A &lt;data item&gt; that is about a collection of intervention durations.</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr"/>
+          <t>An &lt;intervention temporal part duration statistic&gt; that is the average value calculated from a collection of intervention temporal part durations.</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BCIO:050501</t>
+          <t>BCIO:050905</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1327,30 +1354,30 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>minimum intervention duration</t>
-        </is>
-      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>intervention duration statistic</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>An &lt;intervention duration statistic&gt; that is the lowest value from a collection of intervention durations.</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr"/>
+          <t>A &lt;data item&gt; that is about a collection of intervention durations.</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BCIO:050909</t>
+          <t>BCIO:050501</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1361,27 +1388,27 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>mean intervention duration</t>
+          <t>minimum intervention duration</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>An &lt;intervention duration statistic&gt; that is the average value calculated from a collection of intervention durations.</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr"/>
+          <t>An &lt;intervention duration statistic&gt; that is the lowest value from a collection of intervention durations.</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BCIO:050498</t>
+          <t>BCIO:050908</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1392,27 +1419,27 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>median intervention duration</t>
+          <t>maximum intervention duration</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>An &lt;intervention duration statistic&gt; that is the central value of a collection of intervention durations when they are arranged in ascending order.</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr"/>
+          <t>An &lt;intervention duration statistic&gt; that is the highest value from a collection of intervention durations.</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BCIO:050908</t>
+          <t>BCIO:050909</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1423,27 +1450,27 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>maximum intervention duration</t>
+          <t>mean intervention duration</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>An &lt;intervention duration statistic&gt; that is the highest value from a collection of intervention durations.</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr"/>
+          <t>An &lt;intervention duration statistic&gt; that is the average value calculated from a collection of intervention durations.</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BCIO:050506</t>
+          <t>BCIO:050498</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1451,30 +1478,30 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>intervention temporal part duration statistic</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>median intervention duration</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>A &lt;data item&gt; that is about a collection of intervention temporal part durations.</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr"/>
+          <t>An &lt;intervention duration statistic&gt; that is the central value of a collection of intervention durations when they are arranged in ascending order.</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BCIO:050512</t>
+          <t>BCIO:050504</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1482,30 +1509,30 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>median intervention temporal part duration</t>
-        </is>
-      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>total intervention contact event duration</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>An &lt;intervention temporal part duration statistic&gt; that is the central value of a collection of intervention temporal part durations when they are arranged in ascending order.</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr"/>
+          <t>A &lt;data item&gt; that is about the amount of time that the participant is exposed to the intervention through its contact events.</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; 150 minutes; 12 hours</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BCIO:050508</t>
+          <t>BCIO:050910</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1516,27 +1543,27 @@
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>maximum intervention temporal part duration</t>
+          <t>maximum total intervention contact event duration</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>An &lt;intervention temporal part duration statistic&gt; that denotes the highest value from a collection of intervention temporal part durations.</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr"/>
+          <t>A &lt;total intervention contact event duration&gt; that is the highest value from a collection of total contact event durations.</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BCIO:050510</t>
+          <t>BCIO:050495</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1547,27 +1574,27 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>mean intervention temporal part duration</t>
+          <t>mean total intervention contact event duration</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>An &lt;intervention temporal part duration statistic&gt; that is the average value calculated from a collection of intervention temporal part durations.</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr"/>
+          <t>A &lt;total intervention contact event duration&gt; that is the average value calculated from a collection of total contact event durations.</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BCIO:050514</t>
+          <t>BCIO:050499</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1578,27 +1605,27 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>minimum intervention temporal part duration</t>
+          <t>median total intervention contact event duration</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>An &lt;intervention temporal part duration statistic&gt; that denotes the lowest value from a collection of intervention temporal part durations.</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr"/>
+          <t>A &lt;total intervention contact event duration&gt; that is the central value of a collection of total contact event durations when they are arranged in ascending order.</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BCIO:008700</t>
+          <t>BCIO:050503</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1606,35 +1633,30 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>intervention contact event frequency</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>minimum total intervention contact event duration</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>A &lt;data item&gt; about the number times an intervention contact event occurs per unit of time.</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; twice a week; daily; one a week</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>How often intervention sessions or digital contacts are planned to occur</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr"/>
+          <t>A &lt;total intervention contact event duration&gt; that is the lowest value from a collection of total contact event durations.</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BCIO:008515</t>
+          <t>BCIO:050505</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1644,33 +1666,28 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>number of intervention contact events</t>
+          <t>intervention contact event duration statistic</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>A &lt;data item&gt; that is the number of contact events in an intervention temporal part.</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; one; 6; 12; twenty</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>The planned total number of sessions or digital contacts in an intervention or part</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr"/>
+          <t>A &lt;data item&gt; that is about a collection of intervention contact event durations.</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BCIO:050903</t>
+          <t>BCIO:050507</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1678,30 +1695,30 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>intervention contact event frequency statistic</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>maximum intervention contact event duration</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>A &lt;data item&gt; that is about a collection of intervention contact event frequencies.</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr"/>
+          <t>An &lt;intervention contact event duration statistic&gt; that is the highest value from a collection of intervention contact event durations.</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BCIO:050500</t>
+          <t>BCIO:050511</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1712,27 +1729,27 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>minimum intervention contact event frequency</t>
+          <t>median intervention contact event duration</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>An &lt;intervention contact event frequency statistic&gt; that is the lowest value from a collection of intervention contact event frequencies.</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr"/>
+          <t>An &lt;intervention contact event duration statistic&gt; that is the central value of a collection of intervention contact event durations when they are arranged in ascending order.</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BCIO:050906</t>
+          <t>BCIO:050509</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1743,27 +1760,27 @@
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>maximum intervention contact event frequency</t>
+          <t>mean intervention contact event duration</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>An &lt;intervention contact event frequency statistic&gt; that is the highest value from a collection of intervention contact event frequencies.</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr"/>
+          <t>An &lt;intervention contact event duration statistic&gt; that is the average value calculated from a collection of intervention contact event durations.</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BCIO:050496</t>
+          <t>BCIO:050513</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1774,89 +1791,72 @@
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>median intervention contact event frequency</t>
+          <t>minimum intervention contact event duration</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>An &lt;intervention contact event frequency statistic&gt; that is the central value of a collection of  intervention contact event frequencies when they are arranged in ascending order.</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr"/>
+          <t>An &lt;intervention contact event duration statistic&gt; that is the lowest value from a collection of intervention contact event durations.</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BCIO:050911</t>
+          <t>BFO:0000020</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>specifically dependent continuant</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>mean intervention contact event frequency</t>
-        </is>
-      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>An &lt;intervention contact event frequency statistic&gt; that is the average value calculated from a collection of intervention contact event frequencies.</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr"/>
+          <t>b is a specifically dependent continuant = Def. b is a continuant and there is some independent continuant c which is not a spatial region and which is such that b s-depends_on c at every time t during the course of b’s existence. (axiom label in BFO2 Reference: [050-003])</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BCIO:008710</t>
+          <t>PATO:0000044</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>intervention temporal part frequency</t>
-        </is>
-      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>A &lt;data item&gt; that is how often intervention temporal parts occur within an intervention.</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>This is useful when grouping contact events together to the schedule of an intervention. For example, authors may describe participants as taking part in 90 minutes of physical activity weekly. These 90 minutes could be split across several contact events, however together these contact events form an intervention part which occurs weekly. 
-This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; Participants took part in 90 minutes of PA "weekly"</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>How often intervention parts are planned to occur</t>
-        </is>
-      </c>
+          <t>A physical quality which inheres in a bearer by virtue of the number of the bearer's repetitive actions in a particular time.</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
@@ -1903,14 +1903,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>p is a process = Def. p is an occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t. (axiom label in BFO2 Reference: [083-003])</t>
+          <t>An occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BFO:0000144</t>
+          <t>OBI:0000011</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -1918,7 +1918,7 @@
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>process profile</t>
+          <t>planned process</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -1927,14 +1927,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>b is a process_profile =Def. there is some process c such that b process_profile_of c (axiom label in BFO2 Reference: [093-002])</t>
+          <t>A process that realizes a plan which is the concretization of a plan specification.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BCIO:043000</t>
+          <t>BCIO:037000</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -1943,7 +1943,7 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>process attribute</t>
+          <t>intervention</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -1951,14 +1951,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>A process profile that is an attribute of a process.</t>
+          <t>A planned process that has the aim of influencing an outcome.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BCIO:051010</t>
+          <t>BCIO:003000</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -1968,55 +1968,61 @@
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>intervention attribute</t>
+          <t>behaviour change intervention</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>A &lt;process attribute&gt; whose bearer is an intervention.</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr"/>
+          <t>An intervention that has the aim of influencing human behaviour.</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BCIO:009000</t>
+          <t>BCIO:008505</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>intervention temporal part</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>intervention schedule of delivery</t>
-        </is>
-      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>An intervention attribute that is its temporal organisation.</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; Includes the start and end of the BCI and its parts.</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr"/>
+          <t>A &lt;planned process&gt; that is a part of an intervention.</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>A planned part of an intervention</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Temporal parts are defined by the authors of reports. They usually group contact events with similar delivery (e.g. face-to-face), content (e.g. CBT), or contextual features (e.g. school lessons), in order to describe their schedule. 
+This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; counselling sessions; the first 6 weeks of the intervention; group discussion; a presentation; the last 4 weeks of the intervention</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BCIO:008540</t>
+          <t>BCIO:008510</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2024,92 +2030,231 @@
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>intervention contact event</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>irregular intervention schedule</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>An &lt;intervention schedule of delivery&gt; in which the frequency and duration of contact events change over the course of a temporal part or intervention.</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; telephone feedback sessions were more frequent during the first 6 weeks; participants were free to access the app whenever they desired</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>A type of schedule which plans that the duration and frequency of sessions or digital contacts vary across the course of an intervention</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr"/>
+          <t>An &lt;intervention temporal part&gt; that is an occasion in which a member of an intervention population comes into contact with an intervention.</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>All contact events are temporal parts, but not all temporal parts are contact events. Whilst contact events are single continuous events, temporal parts of an intervention can  group together multiple different contact events which might have similar features. For example, a set of 10 counselling sessions might be a temporal part within an intervention. The same intervention can have a set of 5 exercise sessions. These 5 sessions together make up another temporal part. Each single session within these parts  is a contact event.
+This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; A counselling session; An online chat session; An advertisement display.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BCIO:008535</t>
+          <t>BFO:0000144</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>process profile</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>regular intervention schedule</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>An &lt;intervention schedule of delivery&gt; in which the frequency and duration of Intervention temporal parts are uniform across the course of an intervention or intervention part.</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; the length and regularity of sessions were consistent across the duration of the intervention, taking place for an hour each week</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>A type of schedule which plans that the duration and frequency of sessions or digital contacts remain constant across the course of an intervention</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr"/>
+          <t>b is a process_profile =Def. there is some process c such that b process_profile_of c (axiom label in BFO2 Reference: [093-002])</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BCIO:008580</t>
+          <t>BCIO:043000</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>process attribute</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>order of intervention temporal parts</t>
-        </is>
-      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
+          <t>A process profile that is an attribute of a process.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>BCIO:051010</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>intervention attribute</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>A &lt;process attribute&gt; whose bearer is an intervention.</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>BCIO:009000</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>intervention schedule of delivery</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>An intervention attribute that is its temporal organisation.</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; Includes the start and end of the BCI and its parts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>BCIO:008540</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>irregular intervention schedule</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>An &lt;intervention schedule of delivery&gt; in which the frequency and duration of contact events change over the course of a temporal part or intervention.</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>A type of schedule which plans that the duration and frequency of sessions or digital contacts vary across the course of an intervention</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; telephone feedback sessions were more frequent during the first 6 weeks; participants were free to access the app whenever they desired</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>BCIO:008535</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>regular intervention schedule</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>An &lt;intervention schedule of delivery&gt; in which the frequency and duration of Intervention temporal parts are uniform across the course of an intervention or intervention part.</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>A type of schedule which plans that the duration and frequency of sessions or digital contacts remain constant across the course of an intervention</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; the length and regularity of sessions were consistent across the duration of the intervention, taking place for an hour each week</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>BCIO:008580</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>order of intervention temporal parts</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
           <t>An &lt;intervention attribute&gt; that is the  temporal positioning of intervention temporal parts.</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
+      <c r="M61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
         <is>
           <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; "After questionnaires were completed, feedback was selected
 out of a database with messages for each possible combination
@@ -2118,151 +2263,6 @@
 levels to the PA guidelines."</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>OBI:0000011</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>planned process</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>A process that realizes a plan which is the concretization of a plan specification.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>BCIO:008505</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>intervention temporal part</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>A &lt;planned process&gt; that is a part of an intervention.</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>Temporal parts are defined by the authors of reports. They usually group contact events with similar delivery (e.g. face-to-face), content (e.g. CBT), or contextual features (e.g. school lessons), in order to describe their schedule. 
-This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; counselling sessions; the first 6 weeks of the intervention; group discussion; a presentation; the last 4 weeks of the intervention</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>A planned part of an intervention</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>BCIO:008510</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>intervention contact event</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>An &lt;intervention temporal part&gt; that is an occasion in which a member of an intervention population comes into contact with an intervention.</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>All contact events are temporal parts, but not all temporal parts are contact events. Whilst contact events are single continuous events, temporal parts of an intervention can  group together multiple different contact events which might have similar features. For example, a set of 10 counselling sessions might be a temporal part within an intervention. The same intervention can have a set of 5 exercise sessions. These 5 sessions together make up another temporal part. Each single session within these parts  is a contact event.
-This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; A counselling session; An online chat session; An advertisement display.</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>BCIO:037000</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>intervention</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>A planned process that has the aim of influencing an outcome.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>BCIO:003000</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>behaviour change intervention</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>An intervention that has the aim of influencing human behaviour.</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2306,20 +2306,20 @@
           <t>A &lt;temporal region&gt; against which an intervention temporal part is referenced.</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>A statement which describes how the delivery of intervention parts is scheduled relative to associated external events.</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
         <is>
           <t>Temporal references are used by authors when there is a behaviourally relevant event which structures the schedule of a BCI. This can include things like quit dates, childbirth, medical operations etc.
 We often refer to timepoints when we mean a specific time or some extended period (e.g., Monday). This class allows for the natural usage of a term while maintaining ontological coherence.
 This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; A feedback call was scheduled to be delivered around 6 months after the birth of the baby; The smoking intervention started 2 weeks after participants were enrolled into an inpatient setting</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>A statement which describes how the delivery of intervention parts is scheduled relative to associated external events.</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2332,7 +2332,7 @@
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>one-dimensional temporal region</t>
+          <t>temporal interval</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -2344,8 +2344,8 @@
           <t>A one-dimensional temporal region is a temporal region that is extended.</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
     </row>
     <row r="65">
@@ -2371,18 +2371,18 @@
           <t>A &lt;temporal interval&gt; between the end of one intervention temporal part and the beginning of a subsequent intervention temporal part.</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>The planned duration of a break between two parts of an intervention</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
         <is>
           <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; "2 weeks"; "1 day"</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>The planned duration of a break between two parts of an intervention</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2407,18 +2407,18 @@
           <t>A &lt;temporal interval&gt; between the start and end of an intervention temporal part.</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>The planned duration of a part of an intervention</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
         <is>
           <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; 6 weeks; 2 weeks</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>The planned duration of a part of an intervention</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2443,18 +2443,18 @@
           <t>A &lt;temporal interval&gt; between the start and end of an intervention.</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>The planned duration of an intervention</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
         <is>
           <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; 6 weeks; 2 months; 1 year</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>The planned duration of an intervention</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2479,13 +2479,13 @@
           <t>An &lt;temporal interval&gt; between the start and end of an intervention contact event.</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
+      <c r="M68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
         <is>
           <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; 1 hour; 30 minutes; 2 minutes</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Schedule/BCIO-schedule-hierarchy.xlsx
+++ b/Schedule/BCIO-schedule-hierarchy.xlsx
@@ -562,7 +562,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>b is a generically dependent continuant = Def. b is a continuant that g-depends_on one or more other entities. (axiom label in BFO2 Reference: [074-001])</t>
+          <t>A continuant that is dependent on one or other independent continuant bearers. For every instance of A requires some instance of (an independent continuant type) B but which instance of B serves can change from time to time.</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>b is a specifically dependent continuant = Def. b is a continuant and there is some independent continuant c which is not a spatial region and which is such that b s-depends_on c at every time t during the course of b’s existence. (axiom label in BFO2 Reference: [050-003])</t>
+          <t>b is a relational specifically dependent continuant = Def. b is a specifically dependent continuant and there are n &amp;gt; 1 independent continuants c1, … cn which are not spatial regions are such that for all 1  i &amp;lt; j  n, ci  and cj share no common parts, are such that for each 1  i  n, b s-depends_on ci at every time t during the course of b’s existence (axiom label in BFO2 Reference: [131-004])</t>
         </is>
       </c>
     </row>
@@ -2332,7 +2332,7 @@
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>temporal interval</t>
+          <t>one-dimensional temporal region</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
